--- a/draft_guide/Fantasy_Life_2027_Draft_Research.xlsx
+++ b/draft_guide/Fantasy_Life_2027_Draft_Research.xlsx
@@ -10836,19 +10836,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.0905</v>
+        <v>0.2602</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4232</v>
+        <v>0.5366</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7729</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>9.968999999999999</v>
+        <v>9.917</v>
       </c>
       <c r="L5">
         <f>13*N(D5)+MAX(N(E5)-N(D5),0)*Assumptions!$B$24</f>
@@ -10870,11 +10870,11 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.061</v>
+        <v>3.108</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>Top-5 finishes: 2021 (1st) • 2023 (2nd) • 2025 (1st) • 2026 (1st) | recency-weighted score 9.6 [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
       <c r="X5" s="11" t="inlineStr">
@@ -10915,19 +10915,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.0723</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3592</v>
+        <v>0.5766</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7729</v>
+        <v>0.7195</v>
       </c>
       <c r="J6" t="n">
         <v>0.3</v>
       </c>
       <c r="K6" t="n">
-        <v>10.004</v>
+        <v>9.362</v>
       </c>
       <c r="L6">
         <f>13*N(D6)+MAX(N(E6)-N(D6),0)*Assumptions!$B$24</f>
@@ -10949,11 +10949,11 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.038</v>
+        <v>3.257</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>Top-5 finishes: 2021 (3rd) • 2022 (5th) • 2023 (5th) • 2025 (2nd) • 2026 (2nd) | recency-weighted score 6.3 [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
       <c r="X6" s="11" t="inlineStr">
@@ -10994,19 +10994,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.0496</v>
+        <v>0.0726</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2797</v>
+        <v>0.6454</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5563</v>
+        <v>0.5755</v>
       </c>
       <c r="J7" t="n">
         <v>0.3</v>
       </c>
       <c r="K7" t="n">
-        <v>7.575</v>
+        <v>7.65</v>
       </c>
       <c r="L7">
         <f>13*N(D7)+MAX(N(E7)-N(D7),0)*Assumptions!$B$24</f>
@@ -11028,11 +11028,11 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.551</v>
+        <v>3.567</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -11047,7 +11047,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>Top-5 finishes: 2022 (3rd) • 2023 (4th) • 2024 (5th) • 2025 (5th) • 2026 (3rd) | recency-weighted score 4.3 [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
       <c r="X7" s="11" t="inlineStr">
@@ -11073,19 +11073,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.0431</v>
+        <v>0.1194</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2572</v>
+        <v>0.438</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4933</v>
+        <v>0.5461</v>
       </c>
       <c r="J8" t="n">
         <v>0.3</v>
       </c>
       <c r="K8" t="n">
-        <v>6.918</v>
+        <v>7.384</v>
       </c>
       <c r="L8">
         <f>13*N(D8)+MAX(N(E8)-N(D8),0)*Assumptions!$B$24</f>
@@ -11107,11 +11107,11 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.61</v>
+        <v>3.633</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>Top-5 finishes: 2022 (1st) • 2024 (1st) • 2026 (4th) | recency-weighted score 4.5 [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
       <c r="X8" s="11" t="inlineStr">
@@ -11152,19 +11152,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.0431</v>
+        <v>0.0848</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2572</v>
+        <v>0.4595</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4933</v>
+        <v>0.5335</v>
       </c>
       <c r="J9" t="n">
         <v>0.3</v>
       </c>
       <c r="K9" t="n">
-        <v>6.798</v>
+        <v>7.127</v>
       </c>
       <c r="L9">
         <f>13*N(D9)+MAX(N(E9)-N(D9),0)*Assumptions!$B$24</f>
@@ -11186,11 +11186,11 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.592</v>
+        <v>3.624</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -11205,7 +11205,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>Top-5 finishes: 2023 (1st) • 2024 (2nd) • 2026 (5th) | recency-weighted score 3.7 [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
       <c r="X9" s="11" t="inlineStr">
@@ -11217,33 +11217,33 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Chase Briscoe</t>
+          <t>William Byron</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2 wins incl. Las Vegas; 6th</t>
+          <t>2026 Cup Series</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026 title: Kalshi 3.5%</t>
+          <t>2026 title: Kalshi 0.5%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.0405</v>
+        <v>0.0461</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2477</v>
+        <v>0.3811</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4681</v>
+        <v>0.4831</v>
       </c>
       <c r="J10" t="n">
         <v>0.3</v>
       </c>
       <c r="K10" t="n">
-        <v>6.544</v>
+        <v>6.652</v>
       </c>
       <c r="L10">
         <f>13*N(D10)+MAX(N(E10)-N(D10),0)*Assumptions!$B$24</f>
@@ -11265,11 +11265,11 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.595</v>
+        <v>3.643</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -11284,45 +11284,45 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>Top-5 finishes: 2023 (3rd) • 2024 (3rd) • 2025 (4th) | recency-weighted score 2.7 [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
       <c r="X10" s="11" t="inlineStr">
         <is>
-          <t>Jens</t>
+          <t>Korch</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Tyler Reddick</t>
+          <t>Chase Briscoe</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7th, -106</t>
+          <t>2 wins incl. Las Vegas; 6th</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026 title: Kalshi 2.0%</t>
+          <t>2026 title: Kalshi 3.5%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.0385</v>
+        <v>0.0181</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2412</v>
+        <v>0.1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4495</v>
+        <v>0.4729</v>
       </c>
       <c r="J11" t="n">
         <v>0.3</v>
       </c>
       <c r="K11" t="n">
-        <v>6.368</v>
+        <v>6.451</v>
       </c>
       <c r="L11">
         <f>13*N(D11)+MAX(N(E11)-N(D11),0)*Assumptions!$B$24</f>
@@ -11344,11 +11344,11 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.599</v>
+        <v>3.611</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
       <c r="X11" s="11" t="inlineStr">
         <is>
-          <t>Feder</t>
+          <t>Jens</t>
         </is>
       </c>
     </row>
@@ -11389,19 +11389,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.0372</v>
+        <v>0.0224</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2367</v>
+        <v>0.145</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4369</v>
+        <v>0.4465</v>
       </c>
       <c r="J12" t="n">
         <v>0.3</v>
       </c>
       <c r="K12" t="n">
-        <v>6.216</v>
+        <v>6.169</v>
       </c>
       <c r="L12">
         <f>13*N(D12)+MAX(N(E12)-N(D12),0)*Assumptions!$B$24</f>
@@ -11423,11 +11423,11 @@
         <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.553</v>
+        <v>3.577</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>Top-5 finishes: 2021 (4th) • 2022 (4th) | recency-weighted score 0.4 [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
       <c r="X12" s="11" t="inlineStr">
@@ -11454,33 +11454,33 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>Shane van Gisbergen</t>
+          <t>Tyler Reddick</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026 Cup Series</t>
+          <t>7th, -106</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026 title: Kalshi 0.5%</t>
+          <t>2026 title: Kalshi 2.0%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.0366</v>
+        <v>0.0177</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2342</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4303</v>
+        <v>0.4543</v>
       </c>
       <c r="J13" t="n">
         <v>0.3</v>
       </c>
       <c r="K13" t="n">
-        <v>6.194</v>
+        <v>6.269</v>
       </c>
       <c r="L13">
         <f>13*N(D13)+MAX(N(E13)-N(D13),0)*Assumptions!$B$24</f>
@@ -11502,11 +11502,11 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.564</v>
+        <v>3.611</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -11521,19 +11521,19 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
       <c r="X13" s="11" t="inlineStr">
         <is>
-          <t>Mitchell</t>
+          <t>Feder</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>William Byron</t>
+          <t>Shane van Gisbergen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -11547,19 +11547,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.0366</v>
+        <v>0.0173</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2342</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4303</v>
+        <v>0.4351</v>
       </c>
       <c r="J14" t="n">
         <v>0.3</v>
       </c>
       <c r="K14" t="n">
-        <v>6.187</v>
+        <v>6.086</v>
       </c>
       <c r="L14">
         <f>13*N(D14)+MAX(N(E14)-N(D14),0)*Assumptions!$B$24</f>
@@ -11581,11 +11581,11 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>3.579</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -11600,12 +11600,12 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
       <c r="X14" s="11" t="inlineStr">
         <is>
-          <t>Korch</t>
+          <t>Mitchell</t>
         </is>
       </c>
     </row>
@@ -11626,19 +11626,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.0366</v>
+        <v>0.0173</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2342</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4303</v>
+        <v>0.4351</v>
       </c>
       <c r="J15" t="n">
         <v>0.3</v>
       </c>
       <c r="K15" t="n">
-        <v>6.159</v>
+        <v>6.059</v>
       </c>
       <c r="L15">
         <f>13*N(D15)+MAX(N(E15)-N(D15),0)*Assumptions!$B$24</f>
@@ -11660,11 +11660,11 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.573</v>
+        <v>3.583</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
     </row>
@@ -11700,19 +11700,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.0366</v>
+        <v>0.0173</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2342</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4303</v>
+        <v>0.4351</v>
       </c>
       <c r="J16" t="n">
         <v>0.3</v>
       </c>
       <c r="K16" t="n">
-        <v>6.146</v>
+        <v>6.048</v>
       </c>
       <c r="L16">
         <f>13*N(D16)+MAX(N(E16)-N(D16),0)*Assumptions!$B$24</f>
@@ -11734,11 +11734,11 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.558</v>
+        <v>3.573</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -11753,14 +11753,14 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>Alex Bowman</t>
+          <t>AJ Allmendinger</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.0366</v>
+        <v>0.0173</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2342</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4303</v>
+        <v>0.4351</v>
       </c>
       <c r="J17" t="n">
         <v>0.3</v>
       </c>
       <c r="K17" t="n">
-        <v>6.13</v>
+        <v>6.039</v>
       </c>
       <c r="L17">
         <f>13*N(D17)+MAX(N(E17)-N(D17),0)*Assumptions!$B$24</f>
@@ -11808,11 +11808,11 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.588</v>
+        <v>3.563</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -11827,14 +11827,14 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AJ Allmendinger</t>
+          <t>Alex Bowman</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -11848,19 +11848,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.0366</v>
+        <v>0.0173</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2342</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4303</v>
+        <v>0.4351</v>
       </c>
       <c r="J18" t="n">
         <v>0.3</v>
       </c>
       <c r="K18" t="n">
-        <v>6.128</v>
+        <v>6.036</v>
       </c>
       <c r="L18">
         <f>13*N(D18)+MAX(N(E18)-N(D18),0)*Assumptions!$B$24</f>
@@ -11882,11 +11882,11 @@
         <v>4</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.55</v>
+        <v>3.602</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -11901,14 +11901,14 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Todd Gilliland</t>
+          <t>Riley Herbst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -11922,19 +11922,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.0366</v>
+        <v>0.0173</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2342</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4303</v>
+        <v>0.4351</v>
       </c>
       <c r="J19" t="n">
         <v>0.3</v>
       </c>
       <c r="K19" t="n">
-        <v>6.12</v>
+        <v>6.027</v>
       </c>
       <c r="L19">
         <f>13*N(D19)+MAX(N(E19)-N(D19),0)*Assumptions!$B$24</f>
@@ -11956,11 +11956,11 @@
         <v>4</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.553</v>
+        <v>3.565</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -11975,14 +11975,14 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Riley Herbst</t>
+          <t>Ross Chastain</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -11996,19 +11996,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.0366</v>
+        <v>0.0173</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2342</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4303</v>
+        <v>0.4351</v>
       </c>
       <c r="J20" t="n">
         <v>0.3</v>
       </c>
       <c r="K20" t="n">
-        <v>6.12</v>
+        <v>6.024</v>
       </c>
       <c r="L20">
         <f>13*N(D20)+MAX(N(E20)-N(D20),0)*Assumptions!$B$24</f>
@@ -12030,11 +12030,11 @@
         <v>4</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.557</v>
+        <v>3.592</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -12049,14 +12049,19 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
+        </is>
+      </c>
+      <c r="X20" s="11" t="inlineStr">
+        <is>
+          <t>Buckley</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ryan Preece</t>
+          <t>Todd Gilliland</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -12070,19 +12075,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.0366</v>
+        <v>0.0173</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2342</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4303</v>
+        <v>0.4351</v>
       </c>
       <c r="J21" t="n">
         <v>0.3</v>
       </c>
       <c r="K21" t="n">
-        <v>6.109</v>
+        <v>6.018</v>
       </c>
       <c r="L21">
         <f>13*N(D21)+MAX(N(E21)-N(D21),0)*Assumptions!$B$24</f>
@@ -12104,11 +12109,11 @@
         <v>4</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.524</v>
+        <v>3.556</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -12123,14 +12128,14 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ross Chastain</t>
+          <t>Ryan Preece</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -12144,19 +12149,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.0366</v>
+        <v>0.0173</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2342</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4303</v>
+        <v>0.4351</v>
       </c>
       <c r="J22" t="n">
         <v>0.3</v>
       </c>
       <c r="K22" t="n">
-        <v>6.107</v>
+        <v>6.017</v>
       </c>
       <c r="L22">
         <f>13*N(D22)+MAX(N(E22)-N(D22),0)*Assumptions!$B$24</f>
@@ -12178,11 +12183,11 @@
         <v>4</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.575</v>
+        <v>3.53</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -12197,12 +12202,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
-        </is>
-      </c>
-      <c r="X22" s="11" t="inlineStr">
-        <is>
-          <t>Buckley</t>
+          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
     </row>
@@ -12223,19 +12223,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.0366</v>
+        <v>0.0173</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2342</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4303</v>
+        <v>0.4351</v>
       </c>
       <c r="J23" t="n">
         <v>0.3</v>
       </c>
       <c r="K23" t="n">
-        <v>6.104</v>
+        <v>6.008</v>
       </c>
       <c r="L23">
         <f>13*N(D23)+MAX(N(E23)-N(D23),0)*Assumptions!$B$24</f>
@@ -12257,11 +12257,11 @@
         <v>4</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.538</v>
+        <v>3.543</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
       <c r="X23" s="11" t="inlineStr">
@@ -12302,19 +12302,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.0366</v>
+        <v>0.0173</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2342</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4303</v>
+        <v>0.4351</v>
       </c>
       <c r="J24" t="n">
         <v>0.3</v>
       </c>
       <c r="K24" t="n">
-        <v>6.104</v>
+        <v>6.007</v>
       </c>
       <c r="L24">
         <f>13*N(D24)+MAX(N(E24)-N(D24),0)*Assumptions!$B$24</f>
@@ -12336,11 +12336,11 @@
         <v>4</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.542</v>
+        <v>3.552</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -12355,14 +12355,14 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Daniel Suarez</t>
+          <t>Noah Gragson</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -12376,19 +12376,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.0366</v>
+        <v>0.0173</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2342</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4303</v>
+        <v>0.4351</v>
       </c>
       <c r="J25" t="n">
         <v>0.3</v>
       </c>
       <c r="K25" t="n">
-        <v>6.101</v>
+        <v>6.005</v>
       </c>
       <c r="L25">
         <f>13*N(D25)+MAX(N(E25)-N(D25),0)*Assumptions!$B$24</f>
@@ -12410,11 +12410,11 @@
         <v>4</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.535</v>
+        <v>3.561</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -12429,12 +12429,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
-        </is>
-      </c>
-      <c r="X25" s="11" t="inlineStr">
-        <is>
-          <t>Shep</t>
+          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
     </row>
@@ -12455,19 +12450,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.0366</v>
+        <v>0.0173</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2342</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4303</v>
+        <v>0.4351</v>
       </c>
       <c r="J26" t="n">
         <v>0.3</v>
       </c>
       <c r="K26" t="n">
-        <v>6.1</v>
+        <v>6.002</v>
       </c>
       <c r="L26">
         <f>13*N(D26)+MAX(N(E26)-N(D26),0)*Assumptions!$B$24</f>
@@ -12489,11 +12484,11 @@
         <v>4</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.581</v>
+        <v>3.596</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -12508,14 +12503,14 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Noah Gragson</t>
+          <t>Daniel Suarez</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -12529,19 +12524,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.0366</v>
+        <v>0.0173</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2342</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4303</v>
+        <v>0.4351</v>
       </c>
       <c r="J27" t="n">
         <v>0.3</v>
       </c>
       <c r="K27" t="n">
-        <v>6.099</v>
+        <v>6.002</v>
       </c>
       <c r="L27">
         <f>13*N(D27)+MAX(N(E27)-N(D27),0)*Assumptions!$B$24</f>
@@ -12563,11 +12558,11 @@
         <v>4</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.549</v>
+        <v>3.544</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -12582,7 +12577,12 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
+        </is>
+      </c>
+      <c r="X27" s="11" t="inlineStr">
+        <is>
+          <t>Shep</t>
         </is>
       </c>
     </row>
@@ -12603,19 +12603,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.0366</v>
+        <v>0.0173</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2342</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4303</v>
+        <v>0.4351</v>
       </c>
       <c r="J28" t="n">
         <v>0.3</v>
       </c>
       <c r="K28" t="n">
-        <v>6.098</v>
+        <v>5.993</v>
       </c>
       <c r="L28">
         <f>13*N(D28)+MAX(N(E28)-N(D28),0)*Assumptions!$B$24</f>
@@ -12637,11 +12637,11 @@
         <v>4</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.563</v>
+        <v>3.579</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 50%]</t>
+          <t>No 2027 title market yet [v2 certainty adj: sd x2.0, mu shrink 40%, p shrink 30%]</t>
         </is>
       </c>
     </row>
@@ -35955,7 +35955,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Kyle Larson 2026 title: Kalshi 42.0% · EV 12.6 · [Molmen]</t>
+          <t>Kyle Larson 2026 title: Kalshi 42.0% · EV 14.5 · [Molmen]</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -36037,7 +36037,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Denny Hamlin 2026 title: Kalshi 28.0% · EV 12.2 · [Theo]</t>
+          <t>Denny Hamlin 2026 title: Kalshi 28.0% · EV 12.5 · [Theo]</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -36119,7 +36119,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Christopher Bell 2026 title: Kalshi 10.5% · EV 9.3 · [Wu]</t>
+          <t>Christopher Bell 2026 title: Kalshi 10.5% · EV 11.2 · [Wu]</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -36201,7 +36201,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Joey Logano 2026 title: Kalshi 5.5% · EV 8.4 · [Jamzee]</t>
+          <t>Joey Logano 2026 title: Kalshi 5.5% · EV 10.4 · [Jamzee]</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -36283,7 +36283,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Ryan Blaney 2026 title: Kalshi 5.5% · EV 8.3 · [Fryar]</t>
+          <t>Ryan Blaney 2026 title: Kalshi 5.5% · EV 9.9 · [Fryar]</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -36365,7 +36365,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Chase Briscoe 2026 title: Kalshi 3.5% · EV 8.0 · [Jens]</t>
+          <t>William Byron 2026 title: Kalshi 0.5% · EV 8.8 · [Korch]</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -36447,7 +36447,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Tyler Reddick 2026 title: Kalshi 2.0% · EV 7.8 · [Feder]</t>
+          <t>Chase Briscoe 2026 title: Kalshi 3.5% · EV 7.1 · [Jens]</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -36529,7 +36529,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Chase Elliott 2026 title: Kalshi 1.0% · EV 7.6 · [Todd]</t>
+          <t>Chase Elliott 2026 title: Kalshi 1.0% · EV 7.0 · [Todd]</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -36611,7 +36611,7 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Shane van Gisbergen 2026 title: Kalshi 0.5% · EV 7.6 · [Mitchell]</t>
+          <t>Tyler Reddick 2026 title: Kalshi 2.0% · EV 6.9 · [Feder]</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -36693,7 +36693,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>William Byron 2026 title: Kalshi 0.5% · EV 7.6 · [Korch]</t>
+          <t>Shane van Gisbergen 2026 title: Kalshi 0.5% · EV 6.7 · [Mitchell]</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -36775,7 +36775,7 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Michael McDowell 2026 title: Kalshi 0.5% · EV 7.5</t>
+          <t>Michael McDowell 2026 title: Kalshi 0.5% · EV 6.6</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -36857,7 +36857,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Ty Gibbs 2026 title: Kalshi 0.5% · EV 7.5</t>
+          <t>Ty Gibbs 2026 title: Kalshi 0.5% · EV 6.6</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -36939,7 +36939,7 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Alex Bowman 2026 title: Kalshi 0.5% · EV 7.5</t>
+          <t>AJ Allmendinger 2026 title: Kalshi 0.5% · EV 6.6</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -37021,7 +37021,7 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>AJ Allmendinger 2026 title: Kalshi 0.5% · EV 7.5</t>
+          <t>Alex Bowman 2026 title: Kalshi 0.5% · EV 6.6</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
@@ -37103,7 +37103,7 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Todd Gilliland 2026 title: Kalshi 0.5% · EV 7.5</t>
+          <t>Riley Herbst 2026 title: Kalshi 0.5% · EV 6.6</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
@@ -39122,7 +39122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -39161,12 +39161,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Musician</t>
+          <t>NASCAR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ella Langley</t>
+          <t>Kyle Larson</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -39183,12 +39183,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Musician</t>
+          <t>NASCAR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Olivia Rodrigo</t>
+          <t>Denny Hamlin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -39210,7 +39210,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Olivia Dean</t>
+          <t>Ella Langley</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -39232,10 +39232,54 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>confidence-C candidate is in the overall board top 10 — verify before relying</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Musician</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Olivia Dean</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>confidence-C candidate is in the overall board top 10 — verify before relying</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Musician</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Taylor Swift</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>confidence-C candidate is in the overall board top 10 — verify before relying</t>
         </is>
@@ -40035,7 +40079,7 @@
           <t>Detroit Red Wings</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Georgia</t>
         </is>
@@ -40055,7 +40099,7 @@
           <t>Justin Thomas</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>Denny Hamlin</t>
         </is>
@@ -40092,7 +40136,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Georgia (NCAAF, VOR 4.8)</t>
+          <t>Denny Hamlin (NASCAR, VOR 5.5)</t>
         </is>
       </c>
     </row>
@@ -40403,7 +40447,7 @@
           <t>Rory McIlroy</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>Kyle Larson</t>
         </is>
@@ -40423,7 +40467,7 @@
           <t>Jessie Buckley</t>
         </is>
       </c>
-      <c r="N12" s="9" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Taylor Swift</t>
         </is>
@@ -40440,7 +40484,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Taylor Swift (Musician, VOR 6.3)</t>
+          <t>Kyle Larson (NASCAR, VOR 7.5)</t>
         </is>
       </c>
     </row>
@@ -40805,7 +40849,7 @@
         <v/>
       </c>
       <c r="J19" s="10">
-        <f>'NASCAR'!N10</f>
+        <f>'NASCAR'!N11</f>
         <v/>
       </c>
       <c r="K19" s="10">
@@ -40939,7 +40983,7 @@
         <v/>
       </c>
       <c r="J21" s="10">
-        <f>'NASCAR'!N13</f>
+        <f>'NASCAR'!N14</f>
         <v/>
       </c>
       <c r="K21" s="10">
@@ -41006,7 +41050,7 @@
         <v/>
       </c>
       <c r="J22" s="10">
-        <f>'NASCAR'!N25</f>
+        <f>'NASCAR'!N27</f>
         <v/>
       </c>
       <c r="K22" s="10">
@@ -41140,7 +41184,7 @@
         <v/>
       </c>
       <c r="J24" s="10">
-        <f>'NASCAR'!N11</f>
+        <f>'NASCAR'!N13</f>
         <v/>
       </c>
       <c r="K24" s="10">
@@ -41274,7 +41318,7 @@
         <v/>
       </c>
       <c r="J26" s="10">
-        <f>'NASCAR'!N14</f>
+        <f>'NASCAR'!N10</f>
         <v/>
       </c>
       <c r="K26" s="10">
@@ -41475,7 +41519,7 @@
         <v/>
       </c>
       <c r="J29" s="10">
-        <f>'NASCAR'!N22</f>
+        <f>'NASCAR'!N20</f>
         <v/>
       </c>
       <c r="K29" s="10">
@@ -41863,29 +41907,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Musician</t>
+          <t>NASCAR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Olivia Dean</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Kyle Larson</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Molmen</t>
         </is>
       </c>
       <c r="E6">
-        <f>'Musician'!M7</f>
+        <f>'NASCAR'!M5</f>
         <v/>
       </c>
       <c r="F6">
-        <f>'Musician'!N7</f>
+        <f>'NASCAR'!N5</f>
         <v/>
       </c>
       <c r="G6">
-        <f>'Musician'!O7</f>
+        <f>'NASCAR'!O5</f>
         <v/>
       </c>
       <c r="H6" t="n">
@@ -41893,12 +41937,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Grammy EV 10.0</t>
+          <t>2026 title: Kalshi 42.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>'Man I Need' (2026 top 10, 43+ wks per Wikipedia); The Art of Loving</t>
+          <t>2,318 pts, leads Chase after Las Vegas</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -41908,7 +41952,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -41918,7 +41962,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Good but the field reaches for it: let it come to you</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -41933,37 +41977,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Taylor Swift</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Molmen</t>
+          <t>Olivia Dean</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E7">
-        <f>'Musician'!M8</f>
+        <f>'Musician'!M7</f>
         <v/>
       </c>
       <c r="F7">
-        <f>'Musician'!N8</f>
+        <f>'Musician'!N7</f>
         <v/>
       </c>
       <c r="G7">
-        <f>'Musician'!O8</f>
+        <f>'Musician'!O7</f>
         <v/>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Grammy EV 7.7</t>
+          <t>Grammy EV 10.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6 #1 weeks in 2026 (3 songs); 2027 album unannounced</t>
+          <t>'Man I Need' (2026 top 10, 43+ wks per Wikipedia); The Art of Loving</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -41993,52 +42037,52 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Musician</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Taylor Swift</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Korch</t>
+          <t>Molmen</t>
         </is>
       </c>
       <c r="E8">
-        <f>'Country'!M5</f>
+        <f>'Musician'!M8</f>
         <v/>
       </c>
       <c r="F8">
-        <f>'Country'!N5</f>
+        <f>'Musician'!N8</f>
         <v/>
       </c>
       <c r="G8">
-        <f>'Country'!O5</f>
+        <f>'Musician'!O8</f>
         <v/>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IMF WEO Apr-2025: 21.0%</t>
+          <t>Grammy EV 7.7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Oil ramp; IMF paths 20%+ growth</t>
+          <t>6 #1 weeks in 2026 (3 songs); 2027 album unannounced</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
+          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -42046,7 +42090,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Good but the field reaches for it: let it come to you</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -42054,29 +42102,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NCAAB</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Wu</t>
+          <t>Korch</t>
         </is>
       </c>
       <c r="E9">
-        <f>'NCAAB'!M5</f>
+        <f>'Country'!M5</f>
         <v/>
       </c>
       <c r="F9">
-        <f>'NCAAB'!N5</f>
+        <f>'Country'!N5</f>
         <v/>
       </c>
       <c r="G9">
-        <f>'NCAAB'!O5</f>
+        <f>'Country'!O5</f>
         <v/>
       </c>
       <c r="H9" t="n">
@@ -42084,10 +42132,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>+600</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>IMF WEO Apr-2025: 21.0%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Oil ramp; IMF paths 20%+ growth</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>B</t>
@@ -42095,7 +42147,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CBS Sports title odds 2026-08-04</t>
+          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -42103,11 +42155,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>low confidence: far-out event</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
@@ -42115,29 +42163,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NHL</t>
+          <t>NASCAR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Colorado Avalanche</t>
+          <t>Denny Hamlin</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Korch</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="E10">
-        <f>'NHL'!M5</f>
+        <f>'NASCAR'!M6</f>
         <v/>
       </c>
       <c r="F10">
-        <f>'NHL'!N5</f>
+        <f>'NASCAR'!N6</f>
         <v/>
       </c>
       <c r="G10">
-        <f>'NHL'!O5</f>
+        <f>'NASCAR'!O6</f>
         <v/>
       </c>
       <c r="H10" t="n">
@@ -42145,22 +42193,22 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Kalshi 12.5%</t>
+          <t>2026 title: Kalshi 28.0%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>2,278 pts (2nd)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>KXNHL-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNHLEAST/KXNHLWEST-27 Kalshi mid</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -42168,7 +42216,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>low confidence: far-out event</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -42181,24 +42233,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Jens</t>
+          <t>Wu</t>
         </is>
       </c>
       <c r="E11">
-        <f>'NCAAB'!M6</f>
+        <f>'NCAAB'!M5</f>
         <v/>
       </c>
       <c r="F11">
-        <f>'NCAAB'!N6</f>
+        <f>'NCAAB'!N5</f>
         <v/>
       </c>
       <c r="G11">
-        <f>'NCAAB'!O6</f>
+        <f>'NCAAB'!O5</f>
         <v/>
       </c>
       <c r="H11" t="n">
@@ -42237,29 +42289,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NASCAR</t>
+          <t>NHL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kyle Larson</t>
+          <t>Colorado Avalanche</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Molmen</t>
+          <t>Korch</t>
         </is>
       </c>
       <c r="E12">
-        <f>'NASCAR'!M5</f>
+        <f>'NHL'!M5</f>
         <v/>
       </c>
       <c r="F12">
-        <f>'NASCAR'!N5</f>
+        <f>'NHL'!N5</f>
         <v/>
       </c>
       <c r="G12">
-        <f>'NASCAR'!O5</f>
+        <f>'NHL'!O5</f>
         <v/>
       </c>
       <c r="H12" t="n">
@@ -42267,22 +42319,22 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026 title: Kalshi 42.0%</t>
+          <t>Kalshi 12.5%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2,318 pts, leads Chase after Las Vegas</t>
+          <t>West</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>KXNHL-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNHLEAST/KXNHLWEST-27 Kalshi mid</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -42290,11 +42342,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>low confidence: far-out event</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
@@ -42302,29 +42350,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NCAAF</t>
+          <t>NCAAB</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Jens</t>
         </is>
       </c>
       <c r="E13">
-        <f>'NCAAF'!M5</f>
+        <f>'NCAAB'!M6</f>
         <v/>
       </c>
       <c r="F13">
-        <f>'NCAAF'!N5</f>
+        <f>'NCAAB'!N6</f>
         <v/>
       </c>
       <c r="G13">
-        <f>'NCAAF'!O5</f>
+        <f>'NCAAB'!O6</f>
         <v/>
       </c>
       <c r="H13" t="n">
@@ -42332,22 +42380,18 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Kalshi 15.5%</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>AP #2, 5-0, SEC</t>
-        </is>
-      </c>
+          <t>+600</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>KXNCAAF-27 exchange mid-price, pulled 2026-10-08</t>
+          <t>CBS Sports title odds 2026-08-04</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -42355,7 +42399,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>low confidence: far-out event</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
@@ -42363,29 +42411,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NHL</t>
+          <t>NCAAF</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Carolina Hurricanes</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Jamzee</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="E14">
-        <f>'NHL'!M6</f>
+        <f>'NCAAF'!M5</f>
         <v/>
       </c>
       <c r="F14">
-        <f>'NHL'!N6</f>
+        <f>'NCAAF'!N5</f>
         <v/>
       </c>
       <c r="G14">
-        <f>'NHL'!O6</f>
+        <f>'NCAAF'!O5</f>
         <v/>
       </c>
       <c r="H14" t="n">
@@ -42393,12 +42441,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Kalshi 9.5%</t>
+          <t>Kalshi 15.5%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>AP #2, 5-0, SEC</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -42408,7 +42456,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>KXNHL-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNHLEAST/KXNHLWEST-27 Kalshi mid</t>
+          <t>KXNCAAF-27 exchange mid-price, pulled 2026-10-08</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -42424,29 +42472,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>NHL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jannik Sinner</t>
+          <t>Carolina Hurricanes</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Buckley</t>
+          <t>Jamzee</t>
         </is>
       </c>
       <c r="E15">
-        <f>'Tennis'!M5</f>
+        <f>'NHL'!M6</f>
         <v/>
       </c>
       <c r="F15">
-        <f>'Tennis'!N5</f>
+        <f>'NHL'!N6</f>
         <v/>
       </c>
       <c r="G15">
-        <f>'Tennis'!O5</f>
+        <f>'NHL'!O6</f>
         <v/>
       </c>
       <c r="H15" t="n">
@@ -42454,22 +42502,22 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>+100 AO 2027 (pre-injury)</t>
+          <t>Kalshi 9.5%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>ATP 1 (2026-10-08)</t>
+          <t>East</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ATP rank from league standings pull (A) / WTA via Olympics.com Oct 5; AO odds VegasInsider/Johnnybet Oct 2026; probabilities = agent estimates</t>
+          <t>KXNHL-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNHLEAST/KXNHLWEST-27 Kalshi mid</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -42485,29 +42533,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NASCAR</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denny Hamlin</t>
+          <t>Jannik Sinner</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Buckley</t>
         </is>
       </c>
       <c r="E16">
-        <f>'NASCAR'!M6</f>
+        <f>'Tennis'!M5</f>
         <v/>
       </c>
       <c r="F16">
-        <f>'NASCAR'!N6</f>
+        <f>'Tennis'!N5</f>
         <v/>
       </c>
       <c r="G16">
-        <f>'NASCAR'!O6</f>
+        <f>'Tennis'!O5</f>
         <v/>
       </c>
       <c r="H16" t="n">
@@ -42515,22 +42563,22 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026 title: Kalshi 28.0%</t>
+          <t>+100 AO 2027 (pre-injury)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2,278 pts (2nd)</t>
+          <t>ATP 1 (2026-10-08)</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>ATP rank from league standings pull (A) / WTA via Olympics.com Oct 5; AO odds VegasInsider/Johnnybet Oct 2026; probabilities = agent estimates</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -42538,11 +42586,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>low confidence: far-out event</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
@@ -42915,29 +42959,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NCAAF</t>
+          <t>NASCAR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ohio State</t>
+          <t>Christopher Bell</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Mitchell</t>
+          <t>Wu</t>
         </is>
       </c>
       <c r="E23">
-        <f>'NCAAF'!M7</f>
+        <f>'NASCAR'!M7</f>
         <v/>
       </c>
       <c r="F23">
-        <f>'NCAAF'!N7</f>
+        <f>'NASCAR'!N7</f>
         <v/>
       </c>
       <c r="G23">
-        <f>'NCAAF'!O7</f>
+        <f>'NASCAR'!O7</f>
         <v/>
       </c>
       <c r="H23" t="n">
@@ -42945,22 +42989,22 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Kalshi 16.5%</t>
+          <t>2026 title: Kalshi 10.5%</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>AP #5, 4-1, Big Ten</t>
+          <t>2,263 pts (3rd)</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>KXNCAAF-27 exchange mid-price, pulled 2026-10-08</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -42968,7 +43012,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>low confidence: far-out event</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
@@ -42976,29 +43024,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>NCAAF</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Elena Rybakina</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Ohio State</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Mitchell</t>
         </is>
       </c>
       <c r="E24">
-        <f>'Tennis'!M6</f>
+        <f>'NCAAF'!M7</f>
         <v/>
       </c>
       <c r="F24">
-        <f>'Tennis'!N6</f>
+        <f>'NCAAF'!N7</f>
         <v/>
       </c>
       <c r="G24">
-        <f>'Tennis'!O6</f>
+        <f>'NCAAF'!O7</f>
         <v/>
       </c>
       <c r="H24" t="n">
@@ -43006,22 +43054,22 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>+300 AO 2027</t>
+          <t>Kalshi 16.5%</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>WTA 1 (2026-10-08)</t>
+          <t>AP #5, 4-1, Big Ten</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ATP rank from league standings pull (A) / WTA via Olympics.com Oct 5; AO odds VegasInsider/Johnnybet Oct 2026; probabilities = agent estimates</t>
+          <t>KXNCAAF-27 exchange mid-price, pulled 2026-10-08</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -43037,12 +43085,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Actress</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Julianne Moore</t>
+          <t>Elena Rybakina</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -43051,33 +43099,38 @@
         </is>
       </c>
       <c r="E25">
-        <f>'Actress'!M5</f>
+        <f>'Tennis'!M6</f>
         <v/>
       </c>
       <c r="F25">
-        <f>'Actress'!N5</f>
+        <f>'Tennis'!N6</f>
         <v/>
       </c>
       <c r="G25">
-        <f>'Actress'!O5</f>
+        <f>'Tennis'!O6</f>
         <v/>
       </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>+300 AO 2027</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>no 2027 film found in Wikipedia's cast lists</t>
+          <t>WTA 1 (2026-10-08)</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>ATP rank from league standings pull (A) / WTA via Olympics.com Oct 5; AO odds VegasInsider/Johnnybet Oct 2026; probabilities = agent estimates</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -43085,11 +43138,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Good but the field reaches for it: let it come to you</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="n">
@@ -43097,12 +43146,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Actress</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Julianne Moore</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -43111,38 +43160,33 @@
         </is>
       </c>
       <c r="E26">
-        <f>'Country'!M6</f>
+        <f>'Actress'!M5</f>
         <v/>
       </c>
       <c r="F26">
-        <f>'Country'!N6</f>
+        <f>'Actress'!N5</f>
         <v/>
       </c>
       <c r="G26">
-        <f>'Country'!O6</f>
+        <f>'Actress'!O5</f>
         <v/>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>IMF WEO Apr-2025: 15.5%</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>War rebound path; huge uncertainty</t>
+          <t>no 2027 film found in Wikipedia's cast lists</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -43150,7 +43194,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Good but the field reaches for it: let it come to you</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="n">
@@ -43158,47 +43206,52 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rory McIlroy</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>Molmen</t>
+          <t>Sudan</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E27">
-        <f>'Golf'!M6</f>
+        <f>'Country'!M6</f>
         <v/>
       </c>
       <c r="F27">
-        <f>'Golf'!N6</f>
+        <f>'Country'!N6</f>
         <v/>
       </c>
       <c r="G27">
-        <f>'Golf'!O6</f>
+        <f>'Country'!O6</f>
         <v/>
       </c>
       <c r="H27" t="n">
         <v>1</v>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>IMF WEO Apr-2025: 15.5%</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>OWGR 2 (2026-10-08)</t>
+          <t>War rebound path; huge uncertainty</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>OWGR rank from league standings pull (A); major-win probabilities = model (rank-weighted share of 4 majors)</t>
+          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -43214,52 +43267,47 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>Golf</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kansas City Chiefs</t>
+          <t>Rory McIlroy</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Shep</t>
+          <t>Molmen</t>
         </is>
       </c>
       <c r="E28">
-        <f>'NFL'!M5</f>
+        <f>'Golf'!M6</f>
         <v/>
       </c>
       <c r="F28">
-        <f>'NFL'!N5</f>
+        <f>'Golf'!N6</f>
         <v/>
       </c>
       <c r="G28">
-        <f>'NFL'!O5</f>
+        <f>'Golf'!O6</f>
         <v/>
       </c>
       <c r="H28" t="n">
         <v>1</v>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Kalshi 9.5%</t>
-        </is>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>4-0, AFC West</t>
+          <t>OWGR 2 (2026-10-08)</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>KXSB-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNFLAFCCHAMP/KXNFLNFCCHAMP-27 Kalshi mid</t>
+          <t>OWGR rank from league standings pull (A); major-win probabilities = model (rank-weighted share of 4 majors)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -43280,24 +43328,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Buffalo Bills</t>
+          <t>Kansas City Chiefs</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Jens</t>
+          <t>Shep</t>
         </is>
       </c>
       <c r="E29">
-        <f>'NFL'!M6</f>
+        <f>'NFL'!M5</f>
         <v/>
       </c>
       <c r="F29">
-        <f>'NFL'!N6</f>
+        <f>'NFL'!N5</f>
         <v/>
       </c>
       <c r="G29">
-        <f>'NFL'!O6</f>
+        <f>'NFL'!O5</f>
         <v/>
       </c>
       <c r="H29" t="n">
@@ -43305,12 +43353,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Kalshi 10.5%</t>
+          <t>Kalshi 9.5%</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3-1, AFC East</t>
+          <t>4-0, AFC West</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -43336,29 +43384,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Aryna Sabalenka</t>
+          <t>Buffalo Bills</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Fryar</t>
+          <t>Jens</t>
         </is>
       </c>
       <c r="E30">
-        <f>'Tennis'!M7</f>
+        <f>'NFL'!M6</f>
         <v/>
       </c>
       <c r="F30">
-        <f>'Tennis'!N7</f>
+        <f>'NFL'!N6</f>
         <v/>
       </c>
       <c r="G30">
-        <f>'Tennis'!O7</f>
+        <f>'NFL'!O6</f>
         <v/>
       </c>
       <c r="H30" t="n">
@@ -43366,22 +43414,22 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>+175 to +185 AO 2027</t>
+          <t>Kalshi 10.5%</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>WTA 2 (2026-10-08)</t>
+          <t>3-1, AFC East</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>ATP rank from league standings pull (A) / WTA via Olympics.com Oct 5; AO odds VegasInsider/Johnnybet Oct 2026; probabilities = agent estimates</t>
+          <t>KXSB-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNFLAFCCHAMP/KXNFLNFCCHAMP-27 Kalshi mid</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -43397,52 +43445,52 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NCAAF</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Notre Dame</t>
+          <t>Aryna Sabalenka</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Feder</t>
+          <t>Fryar</t>
         </is>
       </c>
       <c r="E31">
-        <f>'NCAAF'!M8</f>
+        <f>'Tennis'!M7</f>
         <v/>
       </c>
       <c r="F31">
-        <f>'NCAAF'!N8</f>
+        <f>'Tennis'!N7</f>
         <v/>
       </c>
       <c r="G31">
-        <f>'NCAAF'!O8</f>
+        <f>'Tennis'!O7</f>
         <v/>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Kalshi 11.5%</t>
+          <t>+175 to +185 AO 2027</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>AP #3, 5-0, Ind</t>
+          <t>WTA 2 (2026-10-08)</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>KXNCAAF-27 exchange mid-price, pulled 2026-10-08</t>
+          <t>ATP rank from league standings pull (A) / WTA via Olympics.com Oct 5; AO odds VegasInsider/Johnnybet Oct 2026; probabilities = agent estimates</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -43458,29 +43506,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>NASCAR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Carlos Alcaraz</t>
+          <t>Joey Logano</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Todd</t>
+          <t>Jamzee</t>
         </is>
       </c>
       <c r="E32">
-        <f>'Tennis'!M8</f>
+        <f>'NASCAR'!M8</f>
         <v/>
       </c>
       <c r="F32">
-        <f>'Tennis'!N8</f>
+        <f>'NASCAR'!N8</f>
         <v/>
       </c>
       <c r="G32">
-        <f>'Tennis'!O8</f>
+        <f>'NASCAR'!O8</f>
         <v/>
       </c>
       <c r="H32" t="n">
@@ -43488,22 +43536,22 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>+150 AO 2027</t>
+          <t>2026 title: Kalshi 5.5%</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>ATP 3 (2026-10-08)</t>
+          <t>2,247 pts (4th)</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>ATP rank from league standings pull (A) / WTA via Olympics.com Oct 5; AO odds VegasInsider/Johnnybet Oct 2026; probabilities = agent estimates</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -43511,7 +43559,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>low confidence: far-out event</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="n">
@@ -43519,42 +43571,42 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>NCAAF</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco 49ers</t>
+          <t>Notre Dame</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Todd</t>
+          <t>Feder</t>
         </is>
       </c>
       <c r="E33">
-        <f>'NFL'!M7</f>
+        <f>'NCAAF'!M8</f>
         <v/>
       </c>
       <c r="F33">
-        <f>'NFL'!N7</f>
+        <f>'NCAAF'!N8</f>
         <v/>
       </c>
       <c r="G33">
-        <f>'NFL'!O7</f>
+        <f>'NCAAF'!O8</f>
         <v/>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Kalshi 9.5%</t>
+          <t>Kalshi 11.5%</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4-0, NFC West</t>
+          <t>AP #3, 5-0, Ind</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -43564,7 +43616,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>KXSB-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNFLAFCCHAMP/KXNFLNFCCHAMP-27 Kalshi mid</t>
+          <t>KXNCAAF-27 exchange mid-price, pulled 2026-10-08</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -43580,47 +43632,52 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Actor</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ryan Gosling</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Carlos Alcaraz</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Todd</t>
         </is>
       </c>
       <c r="E34">
-        <f>'Actor'!M5</f>
+        <f>'Tennis'!M8</f>
         <v/>
       </c>
       <c r="F34">
-        <f>'Actor'!N5</f>
+        <f>'Tennis'!N8</f>
         <v/>
       </c>
       <c r="G34">
-        <f>'Actor'!O5</f>
+        <f>'Tennis'!O8</f>
         <v/>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>+150 AO 2027</t>
+        </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Starfighter (May 28); Avengers: Secret Wars (Dec 17)</t>
+          <t>ATP 3 (2026-10-08)</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>ATP rank from league standings pull (A) / WTA via Olympics.com Oct 5; AO odds VegasInsider/Johnnybet Oct 2026; probabilities = agent estimates</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -43628,11 +43685,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Good but the field reaches for it: let it come to you</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="n">
@@ -43640,12 +43693,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>San Francisco 49ers</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
@@ -43654,15 +43707,15 @@
         </is>
       </c>
       <c r="E35">
-        <f>'Country'!M7</f>
+        <f>'NFL'!M7</f>
         <v/>
       </c>
       <c r="F35">
-        <f>'Country'!N7</f>
+        <f>'NFL'!N7</f>
         <v/>
       </c>
       <c r="G35">
-        <f>'Country'!O7</f>
+        <f>'NFL'!O7</f>
         <v/>
       </c>
       <c r="H35" t="n">
@@ -43670,22 +43723,22 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>IMF WEO Apr-2025: 10.7%</t>
+          <t>Kalshi 9.5%</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Simandou iron-ore ramp</t>
+          <t>4-0, NFC West</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
+          <t>KXSB-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNFLAFCCHAMP/KXNFLNFCCHAMP-27 Kalshi mid</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -43701,52 +43754,47 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>Actor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alexander Zverev</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>Theo</t>
+          <t>Ryan Gosling</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E36">
-        <f>'Tennis'!M9</f>
+        <f>'Actor'!M5</f>
         <v/>
       </c>
       <c r="F36">
-        <f>'Tennis'!N9</f>
+        <f>'Actor'!N5</f>
         <v/>
       </c>
       <c r="G36">
-        <f>'Tennis'!O9</f>
+        <f>'Actor'!O5</f>
         <v/>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>+700 AO 2027</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>ATP 2 (2026-10-08)</t>
+          <t>Starfighter (May 28); Avengers: Secret Wars (Dec 17)</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ATP rank from league standings pull (A) / WTA via Olympics.com Oct 5; AO odds VegasInsider/Johnnybet Oct 2026; probabilities = agent estimates</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -43754,7 +43802,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Good but the field reaches for it: let it come to you</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="n">
@@ -43762,52 +43814,52 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Los Angeles Rams</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Mitchell</t>
+          <t>Todd</t>
         </is>
       </c>
       <c r="E37">
-        <f>'NFL'!M8</f>
+        <f>'Country'!M7</f>
         <v/>
       </c>
       <c r="F37">
-        <f>'NFL'!N8</f>
+        <f>'Country'!N7</f>
         <v/>
       </c>
       <c r="G37">
-        <f>'NFL'!O8</f>
+        <f>'Country'!O7</f>
         <v/>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Kalshi 11.5%</t>
+          <t>IMF WEO Apr-2025: 10.7%</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2-2, NFC West</t>
+          <t>Simandou iron-ore ramp</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>KXSB-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNFLAFCCHAMP/KXNFLNFCCHAMP-27 Kalshi mid</t>
+          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -43823,47 +43875,52 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Actor</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Aaron Pierre</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Alexander Zverev</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Theo</t>
         </is>
       </c>
       <c r="E38">
-        <f>'Actor'!M6</f>
+        <f>'Tennis'!M9</f>
         <v/>
       </c>
       <c r="F38">
-        <f>'Actor'!N6</f>
+        <f>'Tennis'!N9</f>
         <v/>
       </c>
       <c r="G38">
-        <f>'Actor'!O6</f>
+        <f>'Tennis'!O9</f>
         <v/>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>+700 AO 2027</t>
+        </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Starfighter (May 28); Man of Tomorrow (Jul 9)</t>
+          <t>ATP 2 (2026-10-08)</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>ATP rank from league standings pull (A) / WTA via Olympics.com Oct 5; AO odds VegasInsider/Johnnybet Oct 2026; probabilities = agent estimates</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -43871,11 +43928,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Good but the field reaches for it: let it come to you</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="n">
@@ -43883,47 +43936,52 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Los Angeles Rams</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Wu</t>
+          <t>Mitchell</t>
         </is>
       </c>
       <c r="E39">
-        <f>'MLB'!M5</f>
+        <f>'NFL'!M8</f>
         <v/>
       </c>
       <c r="F39">
-        <f>'MLB'!N5</f>
+        <f>'NFL'!N8</f>
         <v/>
       </c>
       <c r="G39">
-        <f>'MLB'!O5</f>
+        <f>'NFL'!O8</f>
         <v/>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Kalshi 11.5%</t>
+        </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026: 100-62 (.6173)</t>
+          <t>2-2, NFC West</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026 win% from league standings (A); title prob = model estimate — no 2027 World Series odds posted</t>
+          <t>KXSB-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNFLAFCCHAMP/KXNFLNFCCHAMP-27 Kalshi mid</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -43931,11 +43989,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>low confidence: far-out event</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="n">
@@ -43943,12 +43997,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>Actor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Matt Fitzpatrick</t>
+          <t>Aaron Pierre</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -43957,15 +44011,15 @@
         </is>
       </c>
       <c r="E40">
-        <f>'Golf'!M7</f>
+        <f>'Actor'!M6</f>
         <v/>
       </c>
       <c r="F40">
-        <f>'Golf'!N7</f>
+        <f>'Actor'!N6</f>
         <v/>
       </c>
       <c r="G40">
-        <f>'Golf'!O7</f>
+        <f>'Actor'!O6</f>
         <v/>
       </c>
       <c r="H40" t="n">
@@ -43973,7 +44027,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>OWGR 3 (2026-10-08)</t>
+          <t>Starfighter (May 28); Man of Tomorrow (Jul 9)</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -43983,7 +44037,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>OWGR rank from league standings pull (A); major-win probabilities = model (rank-weighted share of 4 majors)</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -43991,7 +44045,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Good but the field reaches for it: let it come to you</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="n">
@@ -43999,29 +44057,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NHL</t>
+          <t>NASCAR</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Edmonton Oilers</t>
+          <t>Ryan Blaney</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Buckley</t>
+          <t>Fryar</t>
         </is>
       </c>
       <c r="E41">
-        <f>'NHL'!M8</f>
+        <f>'NASCAR'!M9</f>
         <v/>
       </c>
       <c r="F41">
-        <f>'NHL'!N8</f>
+        <f>'NASCAR'!N9</f>
         <v/>
       </c>
       <c r="G41">
-        <f>'NHL'!O8</f>
+        <f>'NASCAR'!O9</f>
         <v/>
       </c>
       <c r="H41" t="n">
@@ -44029,22 +44087,22 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Kalshi 8.5%</t>
+          <t>2026 title: Kalshi 5.5%</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>2,238 pts (5th)</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>KXNHL-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNHLEAST/KXNHLWEST-27 Kalshi mid</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -44052,7 +44110,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>low confidence: far-out event</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="n">
@@ -44060,29 +44122,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Actor</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Skyler Gisondo</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>Wu</t>
         </is>
       </c>
       <c r="E42">
-        <f>'Actor'!M7</f>
+        <f>'MLB'!M5</f>
         <v/>
       </c>
       <c r="F42">
-        <f>'Actor'!N7</f>
+        <f>'MLB'!N5</f>
         <v/>
       </c>
       <c r="G42">
-        <f>'Actor'!O7</f>
+        <f>'MLB'!O5</f>
         <v/>
       </c>
       <c r="H42" t="n">
@@ -44090,7 +44152,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Man of Tomorrow (Jul 9); Shrek 5 (Jun 30)</t>
+          <t>2026: 100-62 (.6173)</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -44100,7 +44162,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>2026 win% from league standings (A); title prob = model estimate — no 2027 World Series odds posted</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -44110,7 +44172,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Good but the field reaches for it: let it come to you</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -44120,52 +44182,47 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NCAAF</t>
+          <t>Golf</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Miami (FL)</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>Wu</t>
+          <t>Matt Fitzpatrick</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E43">
-        <f>'NCAAF'!M9</f>
+        <f>'Golf'!M7</f>
         <v/>
       </c>
       <c r="F43">
-        <f>'NCAAF'!N9</f>
+        <f>'Golf'!N7</f>
         <v/>
       </c>
       <c r="G43">
-        <f>'NCAAF'!O9</f>
+        <f>'Golf'!O7</f>
         <v/>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Kalshi 10.5%</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>AP #4, 5-0, ACC</t>
+          <t>OWGR 3 (2026-10-08)</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>KXNCAAF-27 exchange mid-price, pulled 2026-10-08</t>
+          <t>OWGR rank from league standings pull (A); major-win probabilities = model (rank-weighted share of 4 majors)</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -44181,47 +44238,52 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Actress</t>
+          <t>NHL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kristen Bell</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Edmonton Oilers</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>Buckley</t>
         </is>
       </c>
       <c r="E44">
-        <f>'Actress'!M6</f>
+        <f>'NHL'!M8</f>
         <v/>
       </c>
       <c r="F44">
-        <f>'Actress'!N6</f>
+        <f>'NHL'!N8</f>
         <v/>
       </c>
       <c r="G44">
-        <f>'Actress'!O6</f>
+        <f>'NHL'!O8</f>
         <v/>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Kalshi 8.5%</t>
+        </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Frozen 3 (Nov 24); Sonic the Hedgehog 4 (Mar 19)</t>
+          <t>West</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>KXNHL-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNHLEAST/KXNHLWEST-27 Kalshi mid</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -44229,11 +44291,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Good but the field reaches for it: let it come to you</t>
-        </is>
-      </c>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="n">
@@ -44241,52 +44299,47 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>Actor</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Baltimore Ravens</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="inlineStr">
-        <is>
-          <t>Wu</t>
+          <t>Skyler Gisondo</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E45">
-        <f>'NFL'!M9</f>
+        <f>'Actor'!M7</f>
         <v/>
       </c>
       <c r="F45">
-        <f>'NFL'!N9</f>
+        <f>'Actor'!N7</f>
         <v/>
       </c>
       <c r="G45">
-        <f>'NFL'!O9</f>
+        <f>'Actor'!O7</f>
         <v/>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Kalshi 7.5%</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>3-1, AFC North</t>
+          <t>Man of Tomorrow (Jul 9); Shrek 5 (Jun 30)</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>KXSB-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNFLAFCCHAMP/KXNFLNFCCHAMP-27 Kalshi mid</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -44294,7 +44347,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Good but the field reaches for it: let it come to you</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="n">
@@ -44302,29 +44359,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NBA</t>
+          <t>NCAAF</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Miami (FL)</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Shep</t>
+          <t>Wu</t>
         </is>
       </c>
       <c r="E46">
-        <f>'NBA'!M9</f>
+        <f>'NCAAF'!M9</f>
         <v/>
       </c>
       <c r="F46">
-        <f>'NBA'!N9</f>
+        <f>'NCAAF'!N9</f>
         <v/>
       </c>
       <c r="G46">
-        <f>'NBA'!O9</f>
+        <f>'NCAAF'!O9</f>
         <v/>
       </c>
       <c r="H46" t="n">
@@ -44332,12 +44389,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Kalshi 4.5%</t>
+          <t>Kalshi 10.5%</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>East; win total 51.5</t>
+          <t>AP #4, 5-0, ACC</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -44347,7 +44404,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>KXNBA-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNBAEAST/KXNBAWEST-27 Kalshi mid</t>
+          <t>KXNCAAF-27 exchange mid-price, pulled 2026-10-08</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -44363,12 +44420,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Actress</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Kristen Bell</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -44377,28 +44434,23 @@
         </is>
       </c>
       <c r="E47">
-        <f>'MLS'!M5</f>
+        <f>'Actress'!M6</f>
         <v/>
       </c>
       <c r="F47">
-        <f>'MLS'!N5</f>
+        <f>'Actress'!N6</f>
         <v/>
       </c>
       <c r="G47">
-        <f>'MLS'!O5</f>
+        <f>'Actress'!O6</f>
         <v/>
       </c>
       <c r="H47" t="n">
         <v>1</v>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2026 Cup: Kalshi 18.0%</t>
-        </is>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026: 60 pts (as of 10-08; season ends Nov 7)</t>
+          <t>Frozen 3 (Nov 24); Sonic the Hedgehog 4 (Mar 19)</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -44408,7 +44460,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -44418,7 +44470,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>low confidence: far-out event</t>
+          <t>Good but the field reaches for it: let it come to you</t>
         </is>
       </c>
     </row>
@@ -44428,48 +44480,52 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NCAAB</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UConn</t>
+          <t>Baltimore Ravens</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Fryar</t>
+          <t>Wu</t>
         </is>
       </c>
       <c r="E48">
-        <f>'NCAAB'!M7</f>
+        <f>'NFL'!M9</f>
         <v/>
       </c>
       <c r="F48">
-        <f>'NCAAB'!N7</f>
+        <f>'NFL'!N9</f>
         <v/>
       </c>
       <c r="G48">
-        <f>'NCAAB'!O7</f>
+        <f>'NFL'!O9</f>
         <v/>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>+1300</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
+          <t>Kalshi 7.5%</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>3-1, AFC North</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CBS Sports title odds 2026-08-04</t>
+          <t>KXSB-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNFLAFCCHAMP/KXNFLNFCCHAMP-27 Kalshi mid</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -44477,11 +44533,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>low confidence: far-out event</t>
-        </is>
-      </c>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="n">
@@ -44489,29 +44541,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NCAAB</t>
+          <t>NBA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Illinois</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>Shep</t>
         </is>
       </c>
       <c r="E49">
-        <f>'NCAAB'!M8</f>
+        <f>'NBA'!M9</f>
         <v/>
       </c>
       <c r="F49">
-        <f>'NCAAB'!N8</f>
+        <f>'NBA'!N9</f>
         <v/>
       </c>
       <c r="G49">
-        <f>'NCAAB'!O8</f>
+        <f>'NBA'!O9</f>
         <v/>
       </c>
       <c r="H49" t="n">
@@ -44519,18 +44571,22 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>+1300</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
+          <t>Kalshi 4.5%</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>East; win total 51.5</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CBS Sports title odds 2026-08-04</t>
+          <t>KXNBA-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNBAEAST/KXNBAWEST-27 Kalshi mid</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -44538,11 +44594,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>low confidence: far-out event</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="n">
@@ -44555,24 +44607,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps FC</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
-        <is>
-          <t>Feder</t>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E50">
-        <f>'MLS'!M6</f>
+        <f>'MLS'!M5</f>
         <v/>
       </c>
       <c r="F50">
-        <f>'MLS'!N6</f>
+        <f>'MLS'!N5</f>
         <v/>
       </c>
       <c r="G50">
-        <f>'MLS'!O6</f>
+        <f>'MLS'!O5</f>
         <v/>
       </c>
       <c r="H50" t="n">
@@ -44580,12 +44632,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026 Cup: Kalshi 23.5%</t>
+          <t>2026 Cup: Kalshi 18.0%</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026: 50 pts (as of 10-08; season ends Nov 7)</t>
+          <t>2026: 60 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -44615,47 +44667,48 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>NCAAB</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cameron Young</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>UConn</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>Fryar</t>
         </is>
       </c>
       <c r="E51">
-        <f>'Golf'!M8</f>
+        <f>'NCAAB'!M7</f>
         <v/>
       </c>
       <c r="F51">
-        <f>'Golf'!N8</f>
+        <f>'NCAAB'!N7</f>
         <v/>
       </c>
       <c r="G51">
-        <f>'Golf'!O8</f>
+        <f>'NCAAB'!O7</f>
         <v/>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>OWGR 4 (2026-10-08)</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>+1300</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>OWGR rank from league standings pull (A); major-win probabilities = model (rank-weighted share of 4 majors)</t>
+          <t>CBS Sports title odds 2026-08-04</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -44663,7 +44716,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>low confidence: far-out event</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -44671,47 +44728,48 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>NCAAB</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>Buckley</t>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E52">
-        <f>'MLB'!M6</f>
+        <f>'NCAAB'!M8</f>
         <v/>
       </c>
       <c r="F52">
-        <f>'MLB'!N6</f>
+        <f>'NCAAB'!N8</f>
         <v/>
       </c>
       <c r="G52">
-        <f>'MLB'!O6</f>
+        <f>'NCAAB'!O8</f>
         <v/>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>2026: 103-59 (.6358)</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>+1300</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026 win% from league standings (A); title prob = model estimate — no 2027 World Series odds posted</t>
+          <t>CBS Sports title odds 2026-08-04</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -44731,37 +44789,42 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Actor</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>John Malkovich</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Vancouver Whitecaps FC</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>Feder</t>
         </is>
       </c>
       <c r="E53">
-        <f>'Actor'!M8</f>
+        <f>'MLS'!M6</f>
         <v/>
       </c>
       <c r="F53">
-        <f>'Actor'!N8</f>
+        <f>'MLS'!N6</f>
         <v/>
       </c>
       <c r="G53">
-        <f>'Actor'!O8</f>
+        <f>'MLS'!O6</f>
         <v/>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026 Cup: Kalshi 23.5%</t>
+        </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>no 2027 film found in Wikipedia's cast lists</t>
+          <t>2026: 50 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -44771,7 +44834,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -44781,7 +44844,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Good but the field reaches for it: let it come to you</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -44791,42 +44854,37 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NASCAR</t>
+          <t>Golf</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Christopher Bell</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>Wu</t>
+          <t>Cameron Young</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E54">
-        <f>'NASCAR'!M7</f>
+        <f>'Golf'!M8</f>
         <v/>
       </c>
       <c r="F54">
-        <f>'NASCAR'!N7</f>
+        <f>'Golf'!N8</f>
         <v/>
       </c>
       <c r="G54">
-        <f>'NASCAR'!O7</f>
+        <f>'Golf'!O8</f>
         <v/>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2026 title: Kalshi 10.5%</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2,263 pts (3rd)</t>
+          <t>OWGR 4 (2026-10-08)</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -44836,7 +44894,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>OWGR rank from league standings pull (A); major-win probabilities = model (rank-weighted share of 4 majors)</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -44844,11 +44902,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>low confidence: far-out event</t>
-        </is>
-      </c>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -44856,37 +44910,42 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>NASCAR</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Wyndham Clark</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>William Byron</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>Korch</t>
         </is>
       </c>
       <c r="E55">
-        <f>'Golf'!M9</f>
+        <f>'NASCAR'!M10</f>
         <v/>
       </c>
       <c r="F55">
-        <f>'Golf'!N9</f>
+        <f>'NASCAR'!N10</f>
         <v/>
       </c>
       <c r="G55">
-        <f>'Golf'!O9</f>
+        <f>'NASCAR'!O10</f>
         <v/>
       </c>
       <c r="H55" t="n">
         <v>2</v>
       </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026 title: Kalshi 0.5%</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>OWGR 5 (2026-10-08)</t>
+          <t>2026 Cup Series</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -44896,7 +44955,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>OWGR rank from league standings pull (A); major-win probabilities = model (rank-weighted share of 4 majors)</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -44904,7 +44963,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>low confidence: far-out event</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -44917,24 +44980,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Jens</t>
+          <t>Buckley</t>
         </is>
       </c>
       <c r="E56">
-        <f>'MLB'!M7</f>
+        <f>'MLB'!M6</f>
         <v/>
       </c>
       <c r="F56">
-        <f>'MLB'!N7</f>
+        <f>'MLB'!N6</f>
         <v/>
       </c>
       <c r="G56">
-        <f>'MLB'!O7</f>
+        <f>'MLB'!O6</f>
         <v/>
       </c>
       <c r="H56" t="n">
@@ -44942,7 +45005,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026: 94-68 (.5776)</t>
+          <t>2026: 103-59 (.6358)</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -44972,52 +45035,47 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>Actor</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle Seahawks</t>
-        </is>
-      </c>
-      <c r="D57" s="11" t="inlineStr">
-        <is>
-          <t>Tim</t>
+          <t>John Malkovich</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E57">
-        <f>'NFL'!M10</f>
+        <f>'Actor'!M8</f>
         <v/>
       </c>
       <c r="F57">
-        <f>'NFL'!N10</f>
+        <f>'Actor'!N8</f>
         <v/>
       </c>
       <c r="G57">
-        <f>'NFL'!O10</f>
+        <f>'Actor'!O8</f>
         <v/>
       </c>
       <c r="H57" t="n">
         <v>2</v>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Kalshi 8.5%</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>3-1, NFC West</t>
+          <t>no 2027 film found in Wikipedia's cast lists</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>KXSB-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNFLAFCCHAMP/KXNFLNFCCHAMP-27 Kalshi mid</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -45025,7 +45083,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Good but the field reaches for it: let it come to you</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -45033,52 +45095,47 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NBA</t>
+          <t>Golf</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="inlineStr">
-        <is>
-          <t>Todd</t>
+          <t>Wyndham Clark</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E58">
-        <f>'NBA'!M10</f>
+        <f>'Golf'!M9</f>
         <v/>
       </c>
       <c r="F58">
-        <f>'NBA'!N10</f>
+        <f>'Golf'!N9</f>
         <v/>
       </c>
       <c r="G58">
-        <f>'NBA'!O10</f>
+        <f>'Golf'!O9</f>
         <v/>
       </c>
       <c r="H58" t="n">
         <v>2</v>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Kalshi 6.5%</t>
-        </is>
-      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>West; win total 48.5</t>
+          <t>OWGR 5 (2026-10-08)</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>KXNBA-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNBAEAST/KXNBAWEST-27 Kalshi mid</t>
+          <t>OWGR rank from league standings pull (A); major-win probabilities = model (rank-weighted share of 4 majors)</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -45094,42 +45151,37 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Inter Miami CF</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Jens</t>
         </is>
       </c>
       <c r="E59">
-        <f>'MLS'!M7</f>
+        <f>'MLB'!M7</f>
         <v/>
       </c>
       <c r="F59">
-        <f>'MLS'!N7</f>
+        <f>'MLB'!N7</f>
         <v/>
       </c>
       <c r="G59">
-        <f>'MLS'!O7</f>
+        <f>'MLB'!O7</f>
         <v/>
       </c>
       <c r="H59" t="n">
         <v>1</v>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2026 Cup: Kalshi 16.5%</t>
-        </is>
-      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026: 46 pts (as of 10-08; season ends Nov 7)</t>
+          <t>2026: 94-68 (.5776)</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -45139,7 +45191,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
+          <t>2026 win% from league standings (A); title prob = model estimate — no 2027 World Series odds posted</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -45159,29 +45211,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NCAAB</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Seattle Seahawks</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Jamzee</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="E60">
-        <f>'NCAAB'!M9</f>
+        <f>'NFL'!M10</f>
         <v/>
       </c>
       <c r="F60">
-        <f>'NCAAB'!N9</f>
+        <f>'NFL'!N10</f>
         <v/>
       </c>
       <c r="G60">
-        <f>'NCAAB'!O9</f>
+        <f>'NFL'!O10</f>
         <v/>
       </c>
       <c r="H60" t="n">
@@ -45189,18 +45241,22 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>+1600</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+          <t>Kalshi 8.5%</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>3-1, NFC West</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CBS Sports title odds 2026-08-04</t>
+          <t>KXSB-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNFLAFCCHAMP/KXNFLNFCCHAMP-27 Kalshi mid</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -45208,11 +45264,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>low confidence: far-out event</t>
-        </is>
-      </c>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -45220,29 +45272,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NCAAF</t>
+          <t>NBA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Jamzee</t>
+          <t>Todd</t>
         </is>
       </c>
       <c r="E61">
-        <f>'NCAAF'!M10</f>
+        <f>'NBA'!M10</f>
         <v/>
       </c>
       <c r="F61">
-        <f>'NCAAF'!N10</f>
+        <f>'NBA'!N10</f>
         <v/>
       </c>
       <c r="G61">
-        <f>'NCAAF'!O10</f>
+        <f>'NBA'!O10</f>
         <v/>
       </c>
       <c r="H61" t="n">
@@ -45250,12 +45302,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Kalshi 9.5%</t>
+          <t>Kalshi 6.5%</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>AP #6, 5-0, SEC</t>
+          <t>West; win total 48.5</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -45265,7 +45317,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>KXNCAAF-27 exchange mid-price, pulled 2026-10-08</t>
+          <t>KXNBA-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNBAEAST/KXNBAWEST-27 Kalshi mid</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -45281,52 +45333,52 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Inter Miami CF</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>Theo</t>
         </is>
       </c>
       <c r="E62">
-        <f>'Country'!M8</f>
+        <f>'MLS'!M7</f>
         <v/>
       </c>
       <c r="F62">
-        <f>'Country'!N8</f>
+        <f>'MLS'!N7</f>
         <v/>
       </c>
       <c r="G62">
-        <f>'Country'!O8</f>
+        <f>'MLS'!O7</f>
         <v/>
       </c>
       <c r="H62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>IMF WEO Apr-2025: 8.2%</t>
+          <t>2026 Cup: Kalshi 16.5%</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Oil start-up</t>
+          <t>2026: 46 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
+          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -45334,7 +45386,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>low confidence: far-out event</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -45342,12 +45398,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NASCAR</t>
+          <t>NCAAB</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Joey Logano</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
@@ -45356,15 +45412,15 @@
         </is>
       </c>
       <c r="E63">
-        <f>'NASCAR'!M8</f>
+        <f>'NCAAB'!M9</f>
         <v/>
       </c>
       <c r="F63">
-        <f>'NASCAR'!N8</f>
+        <f>'NCAAB'!N9</f>
         <v/>
       </c>
       <c r="G63">
-        <f>'NASCAR'!O8</f>
+        <f>'NCAAB'!O9</f>
         <v/>
       </c>
       <c r="H63" t="n">
@@ -45372,22 +45428,18 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026 title: Kalshi 5.5%</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>2,247 pts (4th)</t>
-        </is>
-      </c>
+          <t>+1600</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>CBS Sports title odds 2026-08-04</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -45407,47 +45459,52 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>NCAAF</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>Todd</t>
+          <t>Jamzee</t>
         </is>
       </c>
       <c r="E64">
-        <f>'MLB'!M8</f>
+        <f>'NCAAF'!M10</f>
         <v/>
       </c>
       <c r="F64">
-        <f>'MLB'!N8</f>
+        <f>'NCAAF'!N10</f>
         <v/>
       </c>
       <c r="G64">
-        <f>'MLB'!O8</f>
+        <f>'NCAAF'!O10</f>
         <v/>
       </c>
       <c r="H64" t="n">
         <v>2</v>
       </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Kalshi 9.5%</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026: 94-68 (.5802)</t>
+          <t>AP #6, 5-0, SEC</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026 win% from league standings (A); title prob = model estimate — no 2027 World Series odds posted</t>
+          <t>KXNCAAF-27 exchange mid-price, pulled 2026-10-08</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -45455,11 +45512,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>low confidence: far-out event</t>
-        </is>
-      </c>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -45467,12 +45520,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NHL</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minnesota Wild</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -45481,15 +45534,15 @@
         </is>
       </c>
       <c r="E65">
-        <f>'NHL'!M9</f>
+        <f>'Country'!M8</f>
         <v/>
       </c>
       <c r="F65">
-        <f>'NHL'!N9</f>
+        <f>'Country'!N8</f>
         <v/>
       </c>
       <c r="G65">
-        <f>'NHL'!O9</f>
+        <f>'Country'!O8</f>
         <v/>
       </c>
       <c r="H65" t="n">
@@ -45497,22 +45550,22 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Kalshi 6.5%</t>
+          <t>IMF WEO Apr-2025: 8.2%</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Oil start-up</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>KXNHL-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNHLEAST/KXNHLWEST-27 Kalshi mid</t>
+          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -45528,29 +45581,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Russell Henley</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Jens</t>
+          <t>Todd</t>
         </is>
       </c>
       <c r="E66">
-        <f>'Golf'!M10</f>
+        <f>'MLB'!M8</f>
         <v/>
       </c>
       <c r="F66">
-        <f>'Golf'!N10</f>
+        <f>'MLB'!N8</f>
         <v/>
       </c>
       <c r="G66">
-        <f>'Golf'!O10</f>
+        <f>'MLB'!O8</f>
         <v/>
       </c>
       <c r="H66" t="n">
@@ -45558,7 +45611,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>OWGR 6 (2026-10-08)</t>
+          <t>2026: 94-68 (.5802)</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -45568,7 +45621,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>OWGR rank from league standings pull (A); major-win probabilities = model (rank-weighted share of 4 majors)</t>
+          <t>2026 win% from league standings (A); title prob = model estimate — no 2027 World Series odds posted</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -45576,7 +45629,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>low confidence: far-out event</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -45584,29 +45641,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NASCAR</t>
+          <t>NHL</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ryan Blaney</t>
-        </is>
-      </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>Fryar</t>
+          <t>Minnesota Wild</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E67">
-        <f>'NASCAR'!M9</f>
+        <f>'NHL'!M9</f>
         <v/>
       </c>
       <c r="F67">
-        <f>'NASCAR'!N9</f>
+        <f>'NHL'!N9</f>
         <v/>
       </c>
       <c r="G67">
-        <f>'NASCAR'!O9</f>
+        <f>'NHL'!O9</f>
         <v/>
       </c>
       <c r="H67" t="n">
@@ -45614,22 +45671,22 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026 title: Kalshi 5.5%</t>
+          <t>Kalshi 6.5%</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2,238 pts (5th)</t>
+          <t>West</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>KXNHL-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNHLEAST/KXNHLWEST-27 Kalshi mid</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -45637,11 +45694,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>low confidence: far-out event</t>
-        </is>
-      </c>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -45649,29 +45702,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>Golf</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Russell Henley</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>Jens</t>
         </is>
       </c>
       <c r="E68">
-        <f>'MLB'!M9</f>
+        <f>'Golf'!M10</f>
         <v/>
       </c>
       <c r="F68">
-        <f>'MLB'!N9</f>
+        <f>'Golf'!N10</f>
         <v/>
       </c>
       <c r="G68">
-        <f>'MLB'!O9</f>
+        <f>'Golf'!O10</f>
         <v/>
       </c>
       <c r="H68" t="n">
@@ -45679,7 +45732,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026: 98-64 (.6049)</t>
+          <t>OWGR 6 (2026-10-08)</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -45689,7 +45742,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026 win% from league standings (A); title prob = model estimate — no 2027 World Series odds posted</t>
+          <t>OWGR rank from league standings pull (A); major-win probabilities = model (rank-weighted share of 4 majors)</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -45697,11 +45750,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>low confidence: far-out event</t>
-        </is>
-      </c>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -45709,12 +45758,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -45723,38 +45772,33 @@
         </is>
       </c>
       <c r="E69">
-        <f>'Country'!M9</f>
+        <f>'MLB'!M9</f>
         <v/>
       </c>
       <c r="F69">
-        <f>'Country'!N9</f>
+        <f>'MLB'!N9</f>
         <v/>
       </c>
       <c r="G69">
-        <f>'Country'!O9</f>
+        <f>'MLB'!O9</f>
         <v/>
       </c>
       <c r="H69" t="n">
         <v>2</v>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>IMF WEO Apr-2025: 7.9%</t>
-        </is>
-      </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>LNG expansion</t>
+          <t>2026: 98-64 (.6049)</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
+          <t>2026 win% from league standings (A); title prob = model estimate — no 2027 World Series odds posted</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -45762,7 +45806,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>low confidence: far-out event</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -45770,12 +45818,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Musician</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Harry Styles</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -45784,15 +45832,15 @@
         </is>
       </c>
       <c r="E70">
-        <f>'Musician'!M10</f>
+        <f>'Country'!M9</f>
         <v/>
       </c>
       <c r="F70">
-        <f>'Musician'!N10</f>
+        <f>'Country'!N9</f>
         <v/>
       </c>
       <c r="G70">
-        <f>'Musician'!O10</f>
+        <f>'Country'!O9</f>
         <v/>
       </c>
       <c r="H70" t="n">
@@ -45800,22 +45848,22 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Grammy EV 3.7</t>
+          <t>IMF WEO Apr-2025: 7.9%</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>'Aperture' 1 wk #1 (Feb 2026); 'Kiss All the Time. Disco, Occasionally'</t>
+          <t>LNG expansion</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
+          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -45823,11 +45871,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>Good but the field reaches for it: let it come to you</t>
-        </is>
-      </c>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -45835,37 +45879,42 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Actor</t>
+          <t>Musician</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Matt Damon</t>
-        </is>
-      </c>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>Molmen</t>
+          <t>Harry Styles</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E71">
-        <f>'Actor'!M9</f>
+        <f>'Musician'!M10</f>
         <v/>
       </c>
       <c r="F71">
-        <f>'Actor'!N9</f>
+        <f>'Musician'!N10</f>
         <v/>
       </c>
       <c r="G71">
-        <f>'Actor'!O9</f>
+        <f>'Musician'!O10</f>
         <v/>
       </c>
       <c r="H71" t="n">
         <v>2</v>
       </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Grammy EV 3.7</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Untitled Daniels film (Nov 19)</t>
+          <t>'Aperture' 1 wk #1 (Feb 2026); 'Kiss All the Time. Disco, Occasionally'</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -45875,7 +45924,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -45895,42 +45944,37 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Actor</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>St. Louis City SC</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Matt Damon</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>Molmen</t>
         </is>
       </c>
       <c r="E72">
-        <f>'MLS'!M8</f>
+        <f>'Actor'!M9</f>
         <v/>
       </c>
       <c r="F72">
-        <f>'MLS'!N8</f>
+        <f>'Actor'!N9</f>
         <v/>
       </c>
       <c r="G72">
-        <f>'MLS'!O8</f>
+        <f>'Actor'!O9</f>
         <v/>
       </c>
       <c r="H72" t="n">
         <v>2</v>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2026 Cup: Kalshi 5.5%</t>
-        </is>
-      </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026: 47 pts (as of 10-08; season ends Nov 7)</t>
+          <t>Untitled Daniels film (Nov 19)</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -45940,7 +45984,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -45950,7 +45994,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>low confidence: far-out event</t>
+          <t>Good but the field reaches for it: let it come to you</t>
         </is>
       </c>
     </row>
@@ -45960,37 +46004,42 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jessica Pegula</t>
-        </is>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>Korch</t>
+          <t>St. Louis City SC</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E73">
-        <f>'Tennis'!M10</f>
+        <f>'MLS'!M8</f>
         <v/>
       </c>
       <c r="F73">
-        <f>'Tennis'!N10</f>
+        <f>'MLS'!N8</f>
         <v/>
       </c>
       <c r="G73">
-        <f>'Tennis'!O10</f>
+        <f>'MLS'!O8</f>
         <v/>
       </c>
       <c r="H73" t="n">
         <v>2</v>
       </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026 Cup: Kalshi 5.5%</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>WTA 3 (2026-10-08)</t>
+          <t>2026: 47 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -46000,7 +46049,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>ATP rank from league standings pull (A) / WTA via Olympics.com Oct 5; AO odds VegasInsider/Johnnybet Oct 2026; probabilities = agent estimates</t>
+          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -46008,7 +46057,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>low confidence: far-out event</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -46016,42 +46069,37 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Jessica Pegula</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>Korch</t>
         </is>
       </c>
       <c r="E74">
-        <f>'MLS'!M9</f>
+        <f>'Tennis'!M10</f>
         <v/>
       </c>
       <c r="F74">
-        <f>'MLS'!N9</f>
+        <f>'Tennis'!N10</f>
         <v/>
       </c>
       <c r="G74">
-        <f>'MLS'!O9</f>
+        <f>'Tennis'!O10</f>
         <v/>
       </c>
       <c r="H74" t="n">
         <v>2</v>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2026 Cup: Kalshi 4.5%</t>
-        </is>
-      </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026: 47 pts (as of 10-08; season ends Nov 7)</t>
+          <t>WTA 3 (2026-10-08)</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -46061,7 +46109,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
+          <t>ATP rank from league standings pull (A) / WTA via Olympics.com Oct 5; AO odds VegasInsider/Johnnybet Oct 2026; probabilities = agent estimates</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -46069,11 +46117,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>low confidence: far-out event</t>
-        </is>
-      </c>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -46081,29 +46125,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NASCAR</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chase Briscoe</t>
-        </is>
-      </c>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>Jens</t>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E75">
-        <f>'NASCAR'!M10</f>
+        <f>'MLS'!M9</f>
         <v/>
       </c>
       <c r="F75">
-        <f>'NASCAR'!N10</f>
+        <f>'MLS'!N9</f>
         <v/>
       </c>
       <c r="G75">
-        <f>'NASCAR'!O10</f>
+        <f>'MLS'!O9</f>
         <v/>
       </c>
       <c r="H75" t="n">
@@ -46111,12 +46155,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026 title: Kalshi 3.5%</t>
+          <t>2026 Cup: Kalshi 4.5%</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2 wins incl. Las Vegas; 6th</t>
+          <t>2026: 47 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -46126,7 +46170,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -47412,12 +47456,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tyler Reddick</t>
+          <t>Chase Briscoe</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Feder</t>
+          <t>Jens</t>
         </is>
       </c>
       <c r="E97">
@@ -47437,12 +47481,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026 title: Kalshi 2.0%</t>
+          <t>2026 title: Kalshi 3.5%</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>7th, -106</t>
+          <t>2 wins incl. Las Vegas; 6th</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -47452,7 +47496,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -48810,37 +48854,42 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>NASCAR</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Coco Gauff</t>
+          <t>Chase Elliott</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>Wu</t>
+          <t>Todd</t>
         </is>
       </c>
       <c r="E120">
-        <f>'Tennis'!M12</f>
+        <f>'NASCAR'!M12</f>
         <v/>
       </c>
       <c r="F120">
-        <f>'Tennis'!N12</f>
+        <f>'NASCAR'!N12</f>
         <v/>
       </c>
       <c r="G120">
-        <f>'Tennis'!O12</f>
+        <f>'NASCAR'!O12</f>
         <v/>
       </c>
       <c r="H120" t="n">
         <v>3</v>
       </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2026 title: Kalshi 1.0%</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>WTA 4 (2026-10-08)</t>
+          <t>2026 Cup Series</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -48850,7 +48899,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>ATP rank from league standings pull (A) / WTA via Olympics.com Oct 5; AO odds VegasInsider/Johnnybet Oct 2026; probabilities = agent estimates</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -48858,7 +48907,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>low confidence: far-out event</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -48866,37 +48919,37 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CRCL (Long)</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Coco Gauff</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>Wu</t>
         </is>
       </c>
       <c r="E121">
-        <f>'Stock'!M24</f>
+        <f>'Tennis'!M12</f>
         <v/>
       </c>
       <c r="F121">
-        <f>'Stock'!N24</f>
+        <f>'Tennis'!N12</f>
         <v/>
       </c>
       <c r="G121">
-        <f>'Stock'!O24</f>
+        <f>'Tennis'!O12</f>
         <v/>
       </c>
       <c r="H121" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>stablecoin; rate-cut sensitivity</t>
+          <t>WTA 4 (2026-10-08)</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -48906,7 +48959,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>my estimate: sector view + typical vol; no price data pulled (verify quotes before drafting)</t>
+          <t>ATP rank from league standings pull (A) / WTA via Olympics.com Oct 5; AO odds VegasInsider/Johnnybet Oct 2026; probabilities = agent estimates</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -48914,11 +48967,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>coin flip: take last, no edge</t>
-        </is>
-      </c>
+      <c r="N121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -48931,7 +48980,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>UNH (Long)</t>
+          <t>CRCL (Long)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -48940,15 +48989,15 @@
         </is>
       </c>
       <c r="E122">
-        <f>'Stock'!M25</f>
+        <f>'Stock'!M24</f>
         <v/>
       </c>
       <c r="F122">
-        <f>'Stock'!N25</f>
+        <f>'Stock'!N24</f>
         <v/>
       </c>
       <c r="G122">
-        <f>'Stock'!O25</f>
+        <f>'Stock'!O24</f>
         <v/>
       </c>
       <c r="H122" t="n">
@@ -48956,7 +49005,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>turnaround</t>
+          <t>stablecoin; rate-cut sensitivity</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -48991,24 +49040,24 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>INTC (Long)</t>
-        </is>
-      </c>
-      <c r="D123" s="11" t="inlineStr">
-        <is>
-          <t>Jamzee</t>
+          <t>UNH (Long)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E123">
-        <f>'Stock'!M26</f>
+        <f>'Stock'!M25</f>
         <v/>
       </c>
       <c r="F123">
-        <f>'Stock'!N26</f>
+        <f>'Stock'!N25</f>
         <v/>
       </c>
       <c r="G123">
-        <f>'Stock'!O26</f>
+        <f>'Stock'!O25</f>
         <v/>
       </c>
       <c r="H123" t="n">
@@ -49016,7 +49065,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>foundry / 14A news; +187% in 2026 already</t>
+          <t>turnaround</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -49051,24 +49100,24 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PLTR (Long)</t>
+          <t>INTC (Long)</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>Feder</t>
+          <t>Jamzee</t>
         </is>
       </c>
       <c r="E124">
-        <f>'Stock'!M27</f>
+        <f>'Stock'!M26</f>
         <v/>
       </c>
       <c r="F124">
-        <f>'Stock'!N27</f>
+        <f>'Stock'!N26</f>
         <v/>
       </c>
       <c r="G124">
-        <f>'Stock'!O27</f>
+        <f>'Stock'!O26</f>
         <v/>
       </c>
       <c r="H124" t="n">
@@ -49076,7 +49125,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>momentum; valuation risk</t>
+          <t>foundry / 14A news; +187% in 2026 already</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -49106,37 +49155,37 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Actor</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brian Tyree Henry</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>PLTR (Long)</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>Feder</t>
         </is>
       </c>
       <c r="E125">
-        <f>'Actor'!M11</f>
+        <f>'Stock'!M27</f>
         <v/>
       </c>
       <c r="F125">
-        <f>'Actor'!N11</f>
+        <f>'Stock'!N27</f>
         <v/>
       </c>
       <c r="G125">
-        <f>'Actor'!O11</f>
+        <f>'Stock'!O27</f>
         <v/>
       </c>
       <c r="H125" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Spider-Man: Beyond the Spider-Verse (Jun 18); Panic Carefully (Apr 9)</t>
+          <t>momentum; valuation risk</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -49146,7 +49195,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>my estimate: sector view + typical vol; no price data pulled (verify quotes before drafting)</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -49156,7 +49205,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>TARGET LATE: value the field undervalues</t>
+          <t>coin flip: take last, no edge</t>
         </is>
       </c>
     </row>
@@ -49166,12 +49215,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Actor</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MU (Long)</t>
+          <t>Brian Tyree Henry</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -49180,23 +49229,23 @@
         </is>
       </c>
       <c r="E126">
-        <f>'Stock'!M28</f>
+        <f>'Actor'!M11</f>
         <v/>
       </c>
       <c r="F126">
-        <f>'Stock'!N28</f>
+        <f>'Actor'!N11</f>
         <v/>
       </c>
       <c r="G126">
-        <f>'Stock'!O28</f>
+        <f>'Actor'!O11</f>
         <v/>
       </c>
       <c r="H126" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>HBM4; memory-cycle peak risk</t>
+          <t>Spider-Man: Beyond the Spider-Verse (Jun 18); Panic Carefully (Apr 9)</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -49206,7 +49255,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>my estimate: sector view + typical vol; no price data pulled (verify quotes before drafting)</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -49216,7 +49265,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>coin flip: take last, no edge</t>
+          <t>TARGET LATE: value the field undervalues</t>
         </is>
       </c>
     </row>
@@ -49226,37 +49275,37 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Actress</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Anne Hathaway</t>
-        </is>
-      </c>
-      <c r="D127" s="11" t="inlineStr">
-        <is>
-          <t>Korch</t>
+          <t>MU (Long)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E127">
-        <f>'Actress'!M10</f>
+        <f>'Stock'!M28</f>
         <v/>
       </c>
       <c r="F127">
-        <f>'Actress'!N10</f>
+        <f>'Stock'!N28</f>
         <v/>
       </c>
       <c r="G127">
-        <f>'Actress'!O10</f>
+        <f>'Stock'!O28</f>
         <v/>
       </c>
       <c r="H127" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Alone at Dawn (Dec 25)</t>
+          <t>HBM4; memory-cycle peak risk</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -49266,7 +49315,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>my estimate: sector view + typical vol; no price data pulled (verify quotes before drafting)</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -49276,7 +49325,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Good but the field reaches for it: let it come to you</t>
+          <t>coin flip: take last, no edge</t>
         </is>
       </c>
     </row>
@@ -49286,42 +49335,37 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Actress</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Anne Hathaway</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>Korch</t>
         </is>
       </c>
       <c r="E128">
-        <f>'MLS'!M14</f>
+        <f>'Actress'!M10</f>
         <v/>
       </c>
       <c r="F128">
-        <f>'MLS'!N14</f>
+        <f>'Actress'!N10</f>
         <v/>
       </c>
       <c r="G128">
-        <f>'MLS'!O14</f>
+        <f>'Actress'!O10</f>
         <v/>
       </c>
       <c r="H128" t="n">
-        <v>3</v>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>2026 Cup: Kalshi 2.5%</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>2026: 45 pts (as of 10-08; season ends Nov 7)</t>
+          <t>Alone at Dawn (Dec 25)</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -49331,7 +49375,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -49341,7 +49385,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>low confidence: far-out event</t>
+          <t>Good but the field reaches for it: let it come to you</t>
         </is>
       </c>
     </row>
@@ -49351,37 +49395,42 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>AVGO (Long)</t>
-        </is>
-      </c>
-      <c r="D129" s="11" t="inlineStr">
-        <is>
-          <t>Fryar</t>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E129">
-        <f>'Stock'!M29</f>
+        <f>'MLS'!M14</f>
         <v/>
       </c>
       <c r="F129">
-        <f>'Stock'!N29</f>
+        <f>'MLS'!N14</f>
         <v/>
       </c>
       <c r="G129">
-        <f>'Stock'!O29</f>
+        <f>'MLS'!O14</f>
         <v/>
       </c>
       <c r="H129" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2026 Cup: Kalshi 2.5%</t>
+        </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>custom ASIC demand</t>
+          <t>2026: 45 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -49391,7 +49440,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>my estimate: sector view + typical vol; no price data pulled (verify quotes before drafting)</t>
+          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -49401,7 +49450,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>coin flip: take last, no edge</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -49416,24 +49465,24 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>NEE (Long)</t>
+          <t>AVGO (Long)</t>
         </is>
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>Buckley</t>
+          <t>Fryar</t>
         </is>
       </c>
       <c r="E130">
-        <f>'Stock'!M30</f>
+        <f>'Stock'!M29</f>
         <v/>
       </c>
       <c r="F130">
-        <f>'Stock'!N30</f>
+        <f>'Stock'!N29</f>
         <v/>
       </c>
       <c r="G130">
-        <f>'Stock'!O30</f>
+        <f>'Stock'!O29</f>
         <v/>
       </c>
       <c r="H130" t="n">
@@ -49441,7 +49490,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>owned; no price data pulled</t>
+          <t>custom ASIC demand</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -49451,7 +49500,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>added because a league member currently owns this pick (draft_picks_2026.py); not in the first-pass pool, so figures are placeholders (conf C)</t>
+          <t>my estimate: sector view + typical vol; no price data pulled (verify quotes before drafting)</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -49471,37 +49520,37 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Actress</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Adria Arjona</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>NEE (Long)</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>Buckley</t>
         </is>
       </c>
       <c r="E131">
-        <f>'Actress'!M11</f>
+        <f>'Stock'!M30</f>
         <v/>
       </c>
       <c r="F131">
-        <f>'Actress'!N11</f>
+        <f>'Stock'!N30</f>
         <v/>
       </c>
       <c r="G131">
-        <f>'Actress'!O11</f>
+        <f>'Stock'!O30</f>
         <v/>
       </c>
       <c r="H131" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Man of Tomorrow (Jul 9); The Thomas Crown Affair (Mar 5)</t>
+          <t>owned; no price data pulled</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -49511,7 +49560,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>added because a league member currently owns this pick (draft_picks_2026.py); not in the first-pass pool, so figures are placeholders (conf C)</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -49521,7 +49570,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>TARGET LATE: value the field undervalues</t>
+          <t>coin flip: take last, no edge</t>
         </is>
       </c>
     </row>
@@ -49531,42 +49580,37 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>NASCAR</t>
+          <t>Actress</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Chase Elliott</t>
-        </is>
-      </c>
-      <c r="D132" s="11" t="inlineStr">
-        <is>
-          <t>Todd</t>
+          <t>Adria Arjona</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E132">
-        <f>'NASCAR'!M12</f>
+        <f>'Actress'!M11</f>
         <v/>
       </c>
       <c r="F132">
-        <f>'NASCAR'!N12</f>
+        <f>'Actress'!N11</f>
         <v/>
       </c>
       <c r="G132">
-        <f>'NASCAR'!O12</f>
+        <f>'Actress'!O11</f>
         <v/>
       </c>
       <c r="H132" t="n">
-        <v>3</v>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>2026 title: Kalshi 1.0%</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>2026 Cup Series</t>
+          <t>Man of Tomorrow (Jul 9); The Thomas Crown Affair (Mar 5)</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -49576,7 +49620,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -49586,7 +49630,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>low confidence: far-out event</t>
+          <t>TARGET LATE: value the field undervalues</t>
         </is>
       </c>
     </row>
@@ -49601,12 +49645,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Shane van Gisbergen</t>
+          <t>Tyler Reddick</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>Mitchell</t>
+          <t>Feder</t>
         </is>
       </c>
       <c r="E133">
@@ -49626,12 +49670,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2026 title: Kalshi 0.5%</t>
+          <t>2026 title: Kalshi 2.0%</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>2026 Cup Series</t>
+          <t>7th, -106</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -49641,7 +49685,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -49661,29 +49705,29 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>NASCAR</t>
+          <t>Musician</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>William Byron</t>
-        </is>
-      </c>
-      <c r="D134" s="11" t="inlineStr">
-        <is>
-          <t>Korch</t>
+          <t>Rosalía</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E134">
-        <f>'NASCAR'!M14</f>
+        <f>'Musician'!M12</f>
         <v/>
       </c>
       <c r="F134">
-        <f>'NASCAR'!N14</f>
+        <f>'Musician'!N12</f>
         <v/>
       </c>
       <c r="G134">
-        <f>'NASCAR'!O14</f>
+        <f>'Musician'!O12</f>
         <v/>
       </c>
       <c r="H134" t="n">
@@ -49691,12 +49735,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026 title: Kalshi 0.5%</t>
+          <t>Grammy EV 7.0</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>2026 Cup Series</t>
+          <t>Lux (Grammy-driven pick; small Hot 100 profile)</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -49706,7 +49750,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -49716,7 +49760,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>low confidence: far-out event</t>
+          <t>Overpriced by the field on award buzz: skip</t>
         </is>
       </c>
     </row>
@@ -49726,29 +49770,29 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Musician</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Rosalía</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>Tim</t>
         </is>
       </c>
       <c r="E135">
-        <f>'Musician'!M12</f>
+        <f>'MLS'!M15</f>
         <v/>
       </c>
       <c r="F135">
-        <f>'Musician'!N12</f>
+        <f>'MLS'!N15</f>
         <v/>
       </c>
       <c r="G135">
-        <f>'Musician'!O12</f>
+        <f>'MLS'!O15</f>
         <v/>
       </c>
       <c r="H135" t="n">
@@ -49756,12 +49800,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Grammy EV 7.0</t>
+          <t>2026 Cup: Kalshi 2.5%</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Lux (Grammy-driven pick; small Hot 100 profile)</t>
+          <t>2026: 43 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -49771,7 +49815,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
+          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -49781,7 +49825,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>Overpriced by the field on award buzz: skip</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -49791,42 +49835,37 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Actor</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Charlotte FC</t>
-        </is>
-      </c>
-      <c r="D136" s="11" t="inlineStr">
-        <is>
-          <t>Tim</t>
+          <t>Matt Berry</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E136">
-        <f>'MLS'!M15</f>
+        <f>'Actor'!M12</f>
         <v/>
       </c>
       <c r="F136">
-        <f>'MLS'!N15</f>
+        <f>'Actor'!N12</f>
         <v/>
       </c>
       <c r="G136">
-        <f>'MLS'!O15</f>
+        <f>'Actor'!O12</f>
         <v/>
       </c>
       <c r="H136" t="n">
         <v>3</v>
       </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>2026 Cup: Kalshi 2.5%</t>
-        </is>
-      </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>2026: 43 pts (as of 10-08; season ends Nov 7)</t>
+          <t>Sonic the Hedgehog 4 (Mar 19); A Minecraft Movie Squared (Jul 23)</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -49836,7 +49875,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -49846,7 +49885,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>low confidence: far-out event</t>
+          <t>late filler</t>
         </is>
       </c>
     </row>
@@ -49856,29 +49895,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>NASCAR</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Michael McDowell</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>Mitchell</t>
         </is>
       </c>
       <c r="E137">
-        <f>'NASCAR'!M15</f>
+        <f>'MLS'!M16</f>
         <v/>
       </c>
       <c r="F137">
-        <f>'NASCAR'!N15</f>
+        <f>'MLS'!N16</f>
         <v/>
       </c>
       <c r="G137">
-        <f>'NASCAR'!O15</f>
+        <f>'MLS'!O16</f>
         <v/>
       </c>
       <c r="H137" t="n">
@@ -49886,12 +49925,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026 title: Kalshi 0.5%</t>
+          <t>2026 Cup: Kalshi 3.5%</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>2026 Cup Series</t>
+          <t>2026: 39 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -49901,7 +49940,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -49921,12 +49960,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>NASCAR</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ty Gibbs</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -49935,28 +49974,23 @@
         </is>
       </c>
       <c r="E138">
-        <f>'NASCAR'!M16</f>
+        <f>'MLB'!M13</f>
         <v/>
       </c>
       <c r="F138">
-        <f>'NASCAR'!N16</f>
+        <f>'MLB'!N13</f>
         <v/>
       </c>
       <c r="G138">
-        <f>'NASCAR'!O16</f>
+        <f>'MLB'!O13</f>
         <v/>
       </c>
       <c r="H138" t="n">
         <v>3</v>
       </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>2026 title: Kalshi 0.5%</t>
-        </is>
-      </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>2026 Cup Series</t>
+          <t>2026: 87-75 (.5370)</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -49966,7 +50000,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>2026 win% from league standings (A); title prob = model estimate — no 2027 World Series odds posted</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -49986,12 +50020,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>NASCAR</t>
+          <t>Actor</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Alex Bowman</t>
+          <t>Andrew Scott</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -50000,28 +50034,23 @@
         </is>
       </c>
       <c r="E139">
-        <f>'NASCAR'!M17</f>
+        <f>'Actor'!M13</f>
         <v/>
       </c>
       <c r="F139">
-        <f>'NASCAR'!N17</f>
+        <f>'Actor'!N13</f>
         <v/>
       </c>
       <c r="G139">
-        <f>'NASCAR'!O17</f>
+        <f>'Actor'!O13</f>
         <v/>
       </c>
       <c r="H139" t="n">
         <v>3</v>
       </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>2026 title: Kalshi 0.5%</t>
-        </is>
-      </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>2026 Cup Series</t>
+          <t>Margie Claus (Nov 12); A Place in Hell (Apr 23)</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -50031,7 +50060,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -50041,7 +50070,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>low confidence: far-out event</t>
+          <t>Overpriced by the field on award buzz: skip</t>
         </is>
       </c>
     </row>
@@ -50056,28 +50085,28 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>AJ Allmendinger</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Shane van Gisbergen</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>Mitchell</t>
         </is>
       </c>
       <c r="E140">
-        <f>'NASCAR'!M18</f>
+        <f>'NASCAR'!M14</f>
         <v/>
       </c>
       <c r="F140">
-        <f>'NASCAR'!N18</f>
+        <f>'NASCAR'!N14</f>
         <v/>
       </c>
       <c r="G140">
-        <f>'NASCAR'!O18</f>
+        <f>'NASCAR'!O14</f>
         <v/>
       </c>
       <c r="H140" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -50096,7 +50125,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -50116,12 +50145,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Actor</t>
+          <t>NASCAR</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Matt Berry</t>
+          <t>Michael McDowell</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -50130,23 +50159,28 @@
         </is>
       </c>
       <c r="E141">
-        <f>'Actor'!M12</f>
+        <f>'NASCAR'!M15</f>
         <v/>
       </c>
       <c r="F141">
-        <f>'Actor'!N12</f>
+        <f>'NASCAR'!N15</f>
         <v/>
       </c>
       <c r="G141">
-        <f>'Actor'!O12</f>
+        <f>'NASCAR'!O15</f>
         <v/>
       </c>
       <c r="H141" t="n">
         <v>3</v>
       </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>2026 title: Kalshi 0.5%</t>
+        </is>
+      </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Sonic the Hedgehog 4 (Mar 19); A Minecraft Movie Squared (Jul 23)</t>
+          <t>2026 Cup Series</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -50156,7 +50190,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -50166,7 +50200,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>late filler</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -50181,7 +50215,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Todd Gilliland</t>
+          <t>Ty Gibbs</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -50190,19 +50224,19 @@
         </is>
       </c>
       <c r="E142">
-        <f>'NASCAR'!M19</f>
+        <f>'NASCAR'!M16</f>
         <v/>
       </c>
       <c r="F142">
-        <f>'NASCAR'!N19</f>
+        <f>'NASCAR'!N16</f>
         <v/>
       </c>
       <c r="G142">
-        <f>'NASCAR'!O19</f>
+        <f>'NASCAR'!O16</f>
         <v/>
       </c>
       <c r="H142" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -50221,7 +50255,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -50246,7 +50280,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Riley Herbst</t>
+          <t>AJ Allmendinger</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -50255,19 +50289,19 @@
         </is>
       </c>
       <c r="E143">
-        <f>'NASCAR'!M20</f>
+        <f>'NASCAR'!M17</f>
         <v/>
       </c>
       <c r="F143">
-        <f>'NASCAR'!N20</f>
+        <f>'NASCAR'!N17</f>
         <v/>
       </c>
       <c r="G143">
-        <f>'NASCAR'!O20</f>
+        <f>'NASCAR'!O17</f>
         <v/>
       </c>
       <c r="H143" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -50286,7 +50320,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -50311,7 +50345,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ryan Preece</t>
+          <t>Alex Bowman</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -50320,15 +50354,15 @@
         </is>
       </c>
       <c r="E144">
-        <f>'NASCAR'!M21</f>
+        <f>'NASCAR'!M18</f>
         <v/>
       </c>
       <c r="F144">
-        <f>'NASCAR'!N21</f>
+        <f>'NASCAR'!N18</f>
         <v/>
       </c>
       <c r="G144">
-        <f>'NASCAR'!O21</f>
+        <f>'NASCAR'!O18</f>
         <v/>
       </c>
       <c r="H144" t="n">
@@ -50351,7 +50385,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -50376,24 +50410,24 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ross Chastain</t>
-        </is>
-      </c>
-      <c r="D145" s="11" t="inlineStr">
-        <is>
-          <t>Buckley</t>
+          <t>Riley Herbst</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E145">
-        <f>'NASCAR'!M22</f>
+        <f>'NASCAR'!M19</f>
         <v/>
       </c>
       <c r="F145">
-        <f>'NASCAR'!N22</f>
+        <f>'NASCAR'!N19</f>
         <v/>
       </c>
       <c r="G145">
-        <f>'NASCAR'!O22</f>
+        <f>'NASCAR'!O19</f>
         <v/>
       </c>
       <c r="H145" t="n">
@@ -50416,7 +50450,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -50441,24 +50475,24 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bubba Wallace</t>
+          <t>Ross Chastain</t>
         </is>
       </c>
       <c r="D146" s="11" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Buckley</t>
         </is>
       </c>
       <c r="E146">
-        <f>'NASCAR'!M23</f>
+        <f>'NASCAR'!M20</f>
         <v/>
       </c>
       <c r="F146">
-        <f>'NASCAR'!N23</f>
+        <f>'NASCAR'!N20</f>
         <v/>
       </c>
       <c r="G146">
-        <f>'NASCAR'!O23</f>
+        <f>'NASCAR'!O20</f>
         <v/>
       </c>
       <c r="H146" t="n">
@@ -50481,7 +50515,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -50506,7 +50540,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Zane Smith</t>
+          <t>Todd Gilliland</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -50515,15 +50549,15 @@
         </is>
       </c>
       <c r="E147">
-        <f>'NASCAR'!M24</f>
+        <f>'NASCAR'!M21</f>
         <v/>
       </c>
       <c r="F147">
-        <f>'NASCAR'!N24</f>
+        <f>'NASCAR'!N21</f>
         <v/>
       </c>
       <c r="G147">
-        <f>'NASCAR'!O24</f>
+        <f>'NASCAR'!O21</f>
         <v/>
       </c>
       <c r="H147" t="n">
@@ -50546,7 +50580,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -50571,24 +50605,24 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Daniel Suarez</t>
-        </is>
-      </c>
-      <c r="D148" s="11" t="inlineStr">
-        <is>
-          <t>Shep</t>
+          <t>Ryan Preece</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E148">
-        <f>'NASCAR'!M25</f>
+        <f>'NASCAR'!M22</f>
         <v/>
       </c>
       <c r="F148">
-        <f>'NASCAR'!N25</f>
+        <f>'NASCAR'!N22</f>
         <v/>
       </c>
       <c r="G148">
-        <f>'NASCAR'!O25</f>
+        <f>'NASCAR'!O22</f>
         <v/>
       </c>
       <c r="H148" t="n">
@@ -50611,7 +50645,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -50636,24 +50670,24 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Austin Cindric</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Bubba Wallace</t>
+        </is>
+      </c>
+      <c r="D149" s="11" t="inlineStr">
+        <is>
+          <t>Tim</t>
         </is>
       </c>
       <c r="E149">
-        <f>'NASCAR'!M26</f>
+        <f>'NASCAR'!M23</f>
         <v/>
       </c>
       <c r="F149">
-        <f>'NASCAR'!N26</f>
+        <f>'NASCAR'!N23</f>
         <v/>
       </c>
       <c r="G149">
-        <f>'NASCAR'!O26</f>
+        <f>'NASCAR'!O23</f>
         <v/>
       </c>
       <c r="H149" t="n">
@@ -50676,7 +50710,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -50701,7 +50735,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Noah Gragson</t>
+          <t>Zane Smith</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -50710,15 +50744,15 @@
         </is>
       </c>
       <c r="E150">
-        <f>'NASCAR'!M27</f>
+        <f>'NASCAR'!M24</f>
         <v/>
       </c>
       <c r="F150">
-        <f>'NASCAR'!N27</f>
+        <f>'NASCAR'!N24</f>
         <v/>
       </c>
       <c r="G150">
-        <f>'NASCAR'!O27</f>
+        <f>'NASCAR'!O24</f>
         <v/>
       </c>
       <c r="H150" t="n">
@@ -50741,7 +50775,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -50766,7 +50800,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Carson Hocevar</t>
+          <t>Noah Gragson</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -50775,15 +50809,15 @@
         </is>
       </c>
       <c r="E151">
-        <f>'NASCAR'!M28</f>
+        <f>'NASCAR'!M25</f>
         <v/>
       </c>
       <c r="F151">
-        <f>'NASCAR'!N28</f>
+        <f>'NASCAR'!N25</f>
         <v/>
       </c>
       <c r="G151">
-        <f>'NASCAR'!O28</f>
+        <f>'NASCAR'!O25</f>
         <v/>
       </c>
       <c r="H151" t="n">
@@ -50806,7 +50840,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Kalshi KXNASCARCUPSERIES-NCS26 (2026 champion) shrunk to a 2027 prior; Chase standings via search</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -50826,42 +50860,42 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>NASCAR</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
-        </is>
-      </c>
-      <c r="D152" s="11" t="inlineStr">
-        <is>
-          <t>Mitchell</t>
+          <t>Austin Cindric</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E152">
-        <f>'MLS'!M16</f>
+        <f>'NASCAR'!M26</f>
         <v/>
       </c>
       <c r="F152">
-        <f>'MLS'!N16</f>
+        <f>'NASCAR'!N26</f>
         <v/>
       </c>
       <c r="G152">
-        <f>'MLS'!O16</f>
+        <f>'NASCAR'!O26</f>
         <v/>
       </c>
       <c r="H152" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026 Cup: Kalshi 3.5%</t>
+          <t>2026 title: Kalshi 0.5%</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>2026: 39 pts (as of 10-08; season ends Nov 7)</t>
+          <t>2026 Cup Series</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -50871,7 +50905,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -50891,37 +50925,42 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>NASCAR</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Daniel Suarez</t>
+        </is>
+      </c>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>Shep</t>
         </is>
       </c>
       <c r="E153">
-        <f>'MLB'!M13</f>
+        <f>'NASCAR'!M27</f>
         <v/>
       </c>
       <c r="F153">
-        <f>'MLB'!N13</f>
+        <f>'NASCAR'!N27</f>
         <v/>
       </c>
       <c r="G153">
-        <f>'MLB'!O13</f>
+        <f>'NASCAR'!O27</f>
         <v/>
       </c>
       <c r="H153" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>2026 title: Kalshi 0.5%</t>
+        </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>2026: 87-75 (.5370)</t>
+          <t>2026 Cup Series</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -50931,7 +50970,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026 win% from league standings (A); title prob = model estimate — no 2027 World Series odds posted</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -50951,12 +50990,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Actor</t>
+          <t>NASCAR</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Andrew Scott</t>
+          <t>Carson Hocevar</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -50965,23 +51004,28 @@
         </is>
       </c>
       <c r="E154">
-        <f>'Actor'!M13</f>
+        <f>'NASCAR'!M28</f>
         <v/>
       </c>
       <c r="F154">
-        <f>'Actor'!N13</f>
+        <f>'NASCAR'!N28</f>
         <v/>
       </c>
       <c r="G154">
-        <f>'Actor'!O13</f>
+        <f>'NASCAR'!O28</f>
         <v/>
       </c>
       <c r="H154" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>2026 title: Kalshi 0.5%</t>
+        </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Margie Claus (Nov 12); A Place in Hell (Apr 23)</t>
+          <t>2026 Cup Series</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -50991,7 +51035,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -51001,7 +51045,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>Overpriced by the field on award buzz: skip</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -78208,11 +78252,11 @@
         <v>0.4</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>calendar 2027, no 2027 market; Chase is a lottery</t>
+          <t>calendar 2027, no 2027 market; probabilities now recency-weighted from 2021-26 final standings (lighter p shrink)</t>
         </is>
       </c>
     </row>

--- a/draft_guide/Fantasy_Life_2027_Draft_Research.xlsx
+++ b/draft_guide/Fantasy_Life_2027_Draft_Research.xlsx
@@ -29215,11 +29215,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Grammy EV 13.0</t>
+          <t>Grammy EV 10.8 (raw 12.8, P(cap) 50%)</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>10.78</v>
       </c>
       <c r="I5" t="n">
         <v>12</v>
@@ -29231,7 +29231,7 @@
         <v>8.180999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>13</v>
+        <v>10.78</v>
       </c>
       <c r="M5">
         <f>K5+MIN(L5,Assumptions!$H$14)</f>
@@ -29293,11 +29293,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Grammy EV 10.5</t>
+          <t>Grammy EV 9.3 (raw 10.3, P(cap) 31%)</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.51</v>
+        <v>9.33</v>
       </c>
       <c r="I6" t="n">
         <v>10</v>
@@ -29309,7 +29309,7 @@
         <v>7.332</v>
       </c>
       <c r="L6" t="n">
-        <v>10.51</v>
+        <v>9.33</v>
       </c>
       <c r="M6">
         <f>K6+MIN(L6,Assumptions!$H$14)</f>
@@ -29366,33 +29366,33 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Olivia Dean</t>
+          <t>Taylor Swift</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>'Man I Need' (2026 top 10, 43+ wks per Wikipedia); The Art of Loving</t>
+          <t>6 #1 weeks in 2026 (3 songs); 2027 album unannounced</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Grammy EV 10.0</t>
+          <t>Grammy EV 7.5 (raw 7.8, P(cap) 13%)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.04</v>
+        <v>7.49</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>6.859</v>
+        <v>8.943</v>
       </c>
       <c r="L7" t="n">
-        <v>10.04</v>
+        <v>7.49</v>
       </c>
       <c r="M7">
         <f>K7+MIN(L7,Assumptions!$H$14)</f>
@@ -29410,7 +29410,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.559</v>
+        <v>3.847</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -29429,7 +29429,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Best New Artist won in Feb 2026, so ineligible</t>
+          <t>Showgirl AOTY nom 82%, Fate of Ophelia ROTY nom 88.5% (Kalshi)</t>
         </is>
       </c>
       <c r="V7">
@@ -29440,37 +29440,42 @@
         <f>RANK(V7,$V$5:$V$36)</f>
         <v/>
       </c>
+      <c r="X7" s="11" t="inlineStr">
+        <is>
+          <t>Molmen</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Taylor Swift</t>
+          <t>Olivia Dean</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6 #1 weeks in 2026 (3 songs); 2027 album unannounced</t>
+          <t>'Man I Need' (2026 top 10, 43+ wks per Wikipedia); The Art of Loving</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Grammy EV 7.7</t>
+          <t>Grammy EV 8.7 (raw 9.5, P(cap) 25%)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7.67</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>8.943</v>
+        <v>6.859</v>
       </c>
       <c r="L8" t="n">
-        <v>7.67</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M8">
         <f>K8+MIN(L8,Assumptions!$H$14)</f>
@@ -29488,7 +29493,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.847</v>
+        <v>3.559</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -29507,7 +29512,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Showgirl AOTY nom 82%, Fate of Ophelia ROTY nom 88.5% (Kalshi)</t>
+          <t>Best New Artist won in Feb 2026, so ineligible</t>
         </is>
       </c>
       <c r="V8">
@@ -29518,11 +29523,6 @@
         <f>RANK(V8,$V$5:$V$36)</f>
         <v/>
       </c>
-      <c r="X8" s="11" t="inlineStr">
-        <is>
-          <t>Molmen</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -29537,11 +29537,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Grammy EV 7.3</t>
+          <t>Grammy EV 7.0 (raw 7.2, P(cap) 10%)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.29</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
         <v>10</v>
@@ -29553,7 +29553,7 @@
         <v>7.444</v>
       </c>
       <c r="L9" t="n">
-        <v>7.29</v>
+        <v>7</v>
       </c>
       <c r="M9">
         <f>K9+MIN(L9,Assumptions!$H$14)</f>
@@ -29611,11 +29611,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Grammy EV 3.7</t>
+          <t>Grammy EV 3.8 (raw 3.8, P(cap) 1%)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3.74</v>
+        <v>3.81</v>
       </c>
       <c r="I10" t="n">
         <v>9</v>
@@ -29627,7 +29627,7 @@
         <v>6.974</v>
       </c>
       <c r="L10" t="n">
-        <v>3.74</v>
+        <v>3.81</v>
       </c>
       <c r="M10">
         <f>K10+MIN(L10,Assumptions!$H$14)</f>
@@ -29758,33 +29758,33 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Rosalía</t>
+          <t>BTS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lux (Grammy-driven pick; small Hot 100 profile)</t>
+          <t>Arirang (2026) #1 on the Billboard 200; 'Swim' #1 (Apr 2026); world tour</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Grammy EV 7.0</t>
+          <t>Grammy EV 2.6</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7.01</v>
+        <v>2.6</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K12" t="n">
-        <v>3.046</v>
+        <v>6.905</v>
       </c>
       <c r="L12" t="n">
-        <v>7.01</v>
+        <v>2.6</v>
       </c>
       <c r="M12">
         <f>K12+MIN(L12,Assumptions!$H$14)</f>
@@ -29802,11 +29802,11 @@
         <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.533</v>
+        <v>3.803</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
+          <t>2027 Hot 100 baseline = my estimate; Grammy: estimate (C)</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -29819,7 +29819,11 @@
           <t>C</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Grammy EV is an estimate</t>
+        </is>
+      </c>
       <c r="V12">
         <f>K12+Assumptions!$J$14*MIN(L12,Assumptions!$H$14)</f>
         <v/>
@@ -29828,37 +29832,42 @@
         <f>RANK(V12,$V$5:$V$36)</f>
         <v/>
       </c>
+      <c r="X12" s="11" t="inlineStr">
+        <is>
+          <t>Theo</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>BTS</t>
+          <t>Raye</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Arirang (2026) #1 on the Billboard 200; 'Swim' #1 (Apr 2026); world tour</t>
+          <t>'WHERE IS MY HUSBAND!' ROTY/SOTY nominee</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Grammy EV 2.6</t>
+          <t>Grammy EV 5.8 (raw 5.9, P(cap) 6%)</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.6</v>
+        <v>5.79</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>6.905</v>
+        <v>3.613</v>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>5.79</v>
       </c>
       <c r="M13">
         <f>K13+MIN(L13,Assumptions!$H$14)</f>
@@ -29876,11 +29885,11 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.803</v>
+        <v>1.929</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027 Hot 100 baseline = my estimate; Grammy: estimate (C)</t>
+          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -29893,11 +29902,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Grammy EV is an estimate</t>
-        </is>
-      </c>
+      <c r="U13" t="inlineStr"/>
       <c r="V13">
         <f>K13+Assumptions!$J$14*MIN(L13,Assumptions!$H$14)</f>
         <v/>
@@ -29906,42 +29911,37 @@
         <f>RANK(V13,$V$5:$V$36)</f>
         <v/>
       </c>
-      <c r="X13" s="11" t="inlineStr">
-        <is>
-          <t>Theo</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>Raye</t>
+          <t>Rosalía</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>'WHERE IS MY HUSBAND!' ROTY/SOTY nominee</t>
+          <t>Lux (Grammy-driven pick; small Hot 100 profile)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Grammy EV 5.8</t>
+          <t>Grammy EV 6.2 (raw 6.4, P(cap) 8%)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5.79</v>
+        <v>6.23</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>3.613</v>
+        <v>3.046</v>
       </c>
       <c r="L14" t="n">
-        <v>5.79</v>
+        <v>6.23</v>
       </c>
       <c r="M14">
         <f>K14+MIN(L14,Assumptions!$H$14)</f>
@@ -29959,7 +29959,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.929</v>
+        <v>1.533</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -30063,33 +30063,33 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>Sabrina Carpenter</t>
+          <t>Ariana Grande</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Man's Best Friend (Aug 2025) was last cycle; no successor found</t>
+          <t>'hate that i made you love me' #1 (Jun 2026); SOTY nom 35%</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Grammy EV 1.0</t>
+          <t>Grammy EV 2.7 (raw 2.7, P(cap) 0%)</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2.71</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>6.409</v>
+        <v>4.767</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>2.71</v>
       </c>
       <c r="M16">
         <f>K16+MIN(L16,Assumptions!$H$14)</f>
@@ -30107,11 +30107,11 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.58</v>
+        <v>2.784</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2027 Hot 100 baseline = my estimate; Grammy: estimate (C)</t>
+          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -30133,42 +30133,37 @@
         <f>RANK(V16,$V$5:$V$36)</f>
         <v/>
       </c>
-      <c r="X16" s="11" t="inlineStr">
-        <is>
-          <t>Jens</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>Ariana Grande</t>
+          <t>Sabrina Carpenter</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>'hate that i made you love me' #1 (Jun 2026); SOTY nom 35%</t>
+          <t>Man's Best Friend (Aug 2025) was last cycle; no successor found</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Grammy EV 2.6</t>
+          <t>Grammy EV 1.0</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2.63</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K17" t="n">
-        <v>4.767</v>
+        <v>6.409</v>
       </c>
       <c r="L17" t="n">
-        <v>2.63</v>
+        <v>1</v>
       </c>
       <c r="M17">
         <f>K17+MIN(L17,Assumptions!$H$14)</f>
@@ -30186,11 +30181,11 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.784</v>
+        <v>3.58</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
+          <t>2027 Hot 100 baseline = my estimate; Grammy: estimate (C)</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -30212,6 +30207,11 @@
         <f>RANK(V17,$V$5:$V$36)</f>
         <v/>
       </c>
+      <c r="X17" s="11" t="inlineStr">
+        <is>
+          <t>Jens</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -30305,11 +30305,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Grammy EV 3.9</t>
+          <t>Grammy EV 4.0 (raw 4.0, P(cap) 2%)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.93</v>
+        <v>4.01</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -30321,7 +30321,7 @@
         <v>2.277</v>
       </c>
       <c r="L19" t="n">
-        <v>3.93</v>
+        <v>4.01</v>
       </c>
       <c r="M19">
         <f>K19+MIN(L19,Assumptions!$H$14)</f>
@@ -30537,11 +30537,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Grammy EV 3.0</t>
+          <t>Grammy EV 2.9 (raw 2.9, P(cap) 0%)</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -30553,7 +30553,7 @@
         <v>2.595</v>
       </c>
       <c r="L22" t="n">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="M22">
         <f>K22+MIN(L22,Assumptions!$H$14)</f>
@@ -35975,7 +35975,7 @@
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>Ella Langley Grammy EV 13.0 · EV 21.2</t>
+          <t>Ella Langley Grammy EV 10.8 (raw 12.8, P(cap) 50%) · EV 19.0</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
@@ -36057,7 +36057,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>Olivia Rodrigo Grammy EV 10.5 · EV 17.8 · [Todd]</t>
+          <t>Olivia Rodrigo Grammy EV 9.3 (raw 10.3, P(cap) 31%) · EV 16.7 · [Todd]</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -36139,7 +36139,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>Olivia Dean Grammy EV 10.0 · EV 16.9</t>
+          <t>Taylor Swift Grammy EV 7.5 (raw 7.8, P(cap) 13%) · EV 16.4 · [Molmen]</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -36221,7 +36221,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>Taylor Swift Grammy EV 7.7 · EV 16.6 · [Molmen]</t>
+          <t>Olivia Dean Grammy EV 8.7 (raw 9.5, P(cap) 25%) · EV 15.6</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -36303,7 +36303,7 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Bruno Mars Grammy EV 7.3 · EV 14.7</t>
+          <t>Bruno Mars Grammy EV 7.0 (raw 7.2, P(cap) 10%) · EV 14.4</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
@@ -36385,7 +36385,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>Harry Styles Grammy EV 3.7 · EV 10.7</t>
+          <t>Harry Styles Grammy EV 3.8 (raw 3.8, P(cap) 1%) · EV 10.8</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -36549,7 +36549,7 @@
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
-          <t>Rosalía Grammy EV 7.0 · EV 10.1</t>
+          <t>BTS Grammy EV 2.6 · EV 9.5 · [Theo]</t>
         </is>
       </c>
       <c r="O9" s="5" t="inlineStr">
@@ -36631,7 +36631,7 @@
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
-          <t>BTS Grammy EV 2.6 · EV 9.5 · [Theo]</t>
+          <t>Raye Grammy EV 5.8 (raw 5.9, P(cap) 6%) · EV 9.4</t>
         </is>
       </c>
       <c r="O10" s="5" t="inlineStr">
@@ -36713,7 +36713,7 @@
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
-          <t>Raye Grammy EV 5.8 · EV 9.4</t>
+          <t>Rosalía Grammy EV 6.2 (raw 6.4, P(cap) 8%) · EV 9.3</t>
         </is>
       </c>
       <c r="O11" s="5" t="inlineStr">
@@ -36877,7 +36877,7 @@
       </c>
       <c r="N13" s="5" t="inlineStr">
         <is>
-          <t>Sabrina Carpenter Grammy EV 1.0 · EV 7.4 · [Jens]</t>
+          <t>Ariana Grande Grammy EV 2.7 (raw 2.7, P(cap) 0%) · EV 7.5</t>
         </is>
       </c>
       <c r="O13" s="5" t="inlineStr">
@@ -36959,7 +36959,7 @@
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
-          <t>Ariana Grande Grammy EV 2.6 · EV 7.4</t>
+          <t>Sabrina Carpenter Grammy EV 1.0 · EV 7.4 · [Jens]</t>
         </is>
       </c>
       <c r="O14" s="5" t="inlineStr">
@@ -37123,7 +37123,7 @@
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>Phoebe Bridgers Grammy EV 3.9 · EV 6.2</t>
+          <t>Phoebe Bridgers Grammy EV 4.0 (raw 4.0, P(cap) 2%) · EV 6.3</t>
         </is>
       </c>
       <c r="O16" s="6" t="inlineStr">
@@ -39254,7 +39254,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Olivia Dean</t>
+          <t>Taylor Swift</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -39276,7 +39276,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Taylor Swift</t>
+          <t>Olivia Dean</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -39875,7 +39875,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Olivia Rodrigo (Musician, VOR 7.6)</t>
+          <t>Olivia Rodrigo (Musician, VOR 6.4)</t>
         </is>
       </c>
     </row>
@@ -40865,7 +40865,7 @@
         <v/>
       </c>
       <c r="N19" s="10">
-        <f>'Musician'!N16</f>
+        <f>'Musician'!N17</f>
         <v/>
       </c>
       <c r="O19" s="10">
@@ -41133,7 +41133,7 @@
         <v/>
       </c>
       <c r="N23" s="10">
-        <f>'Musician'!N13</f>
+        <f>'Musician'!N12</f>
         <v/>
       </c>
       <c r="O23" s="10">
@@ -41401,7 +41401,7 @@
         <v/>
       </c>
       <c r="N27" s="10">
-        <f>'Musician'!N8</f>
+        <f>'Musician'!N7</f>
         <v/>
       </c>
       <c r="O27" s="10">
@@ -41716,29 +41716,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Musician</t>
+          <t>NBA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ella Langley</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Wu</t>
         </is>
       </c>
       <c r="E3">
-        <f>'Musician'!M5</f>
+        <f>'NBA'!M6</f>
         <v/>
       </c>
       <c r="F3">
-        <f>'Musician'!N5</f>
+        <f>'NBA'!N6</f>
         <v/>
       </c>
       <c r="G3">
-        <f>'Musician'!O5</f>
+        <f>'NBA'!O6</f>
         <v/>
       </c>
       <c r="H3" t="n">
@@ -41746,22 +41746,22 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Grammy EV 13.0</t>
+          <t>Kalshi 21.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>'Choosin' Texas' 24 wks #1 in 2026 (record run); top-10 tail into 2027; 'Dandelion' album</t>
+          <t>West; win total 59.5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
+          <t>KXNBA-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNBAEAST/KXNBAWEST-27 Kalshi mid</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -41769,11 +41769,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Good but the field reaches for it: let it come to you</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="9" t="n">
@@ -41781,29 +41777,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NBA</t>
+          <t>Musician</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Wu</t>
+          <t>Ella Langley</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E4">
-        <f>'NBA'!M6</f>
+        <f>'Musician'!M5</f>
         <v/>
       </c>
       <c r="F4">
-        <f>'NBA'!N6</f>
+        <f>'Musician'!N5</f>
         <v/>
       </c>
       <c r="G4">
-        <f>'NBA'!O6</f>
+        <f>'Musician'!O5</f>
         <v/>
       </c>
       <c r="H4" t="n">
@@ -41811,22 +41807,22 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Kalshi 21.5%</t>
+          <t>Grammy EV 10.8 (raw 12.8, P(cap) 50%)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>West; win total 59.5</t>
+          <t>'Choosin' Texas' 24 wks #1 in 2026 (record run); top-10 tail into 2027; 'Dandelion' album</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>KXNBA-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNBAEAST/KXNBAWEST-27 Kalshi mid</t>
+          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -41834,7 +41830,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Good but the field reaches for it: let it come to you</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -41842,29 +41842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Musician</t>
+          <t>NASCAR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Olivia Rodrigo</t>
+          <t>Kyle Larson</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Todd</t>
+          <t>Molmen</t>
         </is>
       </c>
       <c r="E5">
-        <f>'Musician'!M6</f>
+        <f>'NASCAR'!M5</f>
         <v/>
       </c>
       <c r="F5">
-        <f>'Musician'!N6</f>
+        <f>'NASCAR'!N5</f>
         <v/>
       </c>
       <c r="G5">
-        <f>'Musician'!O6</f>
+        <f>'NASCAR'!O5</f>
         <v/>
       </c>
       <c r="H5" t="n">
@@ -41872,12 +41872,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Grammy EV 10.5</t>
+          <t>2026 title: Kalshi 42.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026 #1 'drop dead' (1 wk) + top-10 songs; AOTY frontrunner album</t>
+          <t>2,318 pts, leads Chase after Las Vegas</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -41887,7 +41887,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -41897,7 +41897,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Good but the field reaches for it: let it come to you</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -41907,29 +41907,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NASCAR</t>
+          <t>Musician</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kyle Larson</t>
+          <t>Olivia Rodrigo</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Molmen</t>
+          <t>Todd</t>
         </is>
       </c>
       <c r="E6">
-        <f>'NASCAR'!M5</f>
+        <f>'Musician'!M6</f>
         <v/>
       </c>
       <c r="F6">
-        <f>'NASCAR'!N5</f>
+        <f>'Musician'!N6</f>
         <v/>
       </c>
       <c r="G6">
-        <f>'NASCAR'!O5</f>
+        <f>'Musician'!O6</f>
         <v/>
       </c>
       <c r="H6" t="n">
@@ -41937,12 +41937,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026 title: Kalshi 42.0%</t>
+          <t>Grammy EV 9.3 (raw 10.3, P(cap) 31%)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2,318 pts, leads Chase after Las Vegas</t>
+          <t>2026 #1 'drop dead' (1 wk) + top-10 songs; AOTY frontrunner album</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
+          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -41962,7 +41962,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>low confidence: far-out event</t>
+          <t>Good but the field reaches for it: let it come to you</t>
         </is>
       </c>
     </row>
@@ -41977,12 +41977,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Olivia Dean</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Taylor Swift</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Molmen</t>
         </is>
       </c>
       <c r="E7">
@@ -42002,12 +42002,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Grammy EV 10.0</t>
+          <t>Grammy EV 7.5 (raw 7.8, P(cap) 13%)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>'Man I Need' (2026 top 10, 43+ wks per Wikipedia); The Art of Loving</t>
+          <t>6 #1 weeks in 2026 (3 songs); 2027 album unannounced</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -42037,52 +42037,52 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Musician</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Taylor Swift</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Molmen</t>
+          <t>Korch</t>
         </is>
       </c>
       <c r="E8">
-        <f>'Musician'!M8</f>
+        <f>'Country'!M5</f>
         <v/>
       </c>
       <c r="F8">
-        <f>'Musician'!N8</f>
+        <f>'Country'!N5</f>
         <v/>
       </c>
       <c r="G8">
-        <f>'Musician'!O8</f>
+        <f>'Country'!O5</f>
         <v/>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Grammy EV 7.7</t>
+          <t>IMF WEO Apr-2025: 21.0%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6 #1 weeks in 2026 (3 songs); 2027 album unannounced</t>
+          <t>Oil ramp; IMF paths 20%+ growth</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
+          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -42090,11 +42090,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Good but the field reaches for it: let it come to you</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -42102,29 +42098,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>NASCAR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Denny Hamlin</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Korch</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="E9">
-        <f>'Country'!M5</f>
+        <f>'NASCAR'!M6</f>
         <v/>
       </c>
       <c r="F9">
-        <f>'Country'!N5</f>
+        <f>'NASCAR'!N6</f>
         <v/>
       </c>
       <c r="G9">
-        <f>'Country'!O5</f>
+        <f>'NASCAR'!O6</f>
         <v/>
       </c>
       <c r="H9" t="n">
@@ -42132,22 +42128,22 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IMF WEO Apr-2025: 21.0%</t>
+          <t>2026 title: Kalshi 28.0%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Oil ramp; IMF paths 20%+ growth</t>
+          <t>2,278 pts (2nd)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -42155,7 +42151,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>low confidence: far-out event</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
@@ -42163,42 +42163,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NASCAR</t>
+          <t>Musician</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denny Hamlin</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>Theo</t>
+          <t>Olivia Dean</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E10">
-        <f>'NASCAR'!M6</f>
+        <f>'Musician'!M8</f>
         <v/>
       </c>
       <c r="F10">
-        <f>'NASCAR'!N6</f>
+        <f>'Musician'!N8</f>
         <v/>
       </c>
       <c r="G10">
-        <f>'NASCAR'!O6</f>
+        <f>'Musician'!O8</f>
         <v/>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026 title: Kalshi 28.0%</t>
+          <t>Grammy EV 8.7 (raw 9.5, P(cap) 25%)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2,278 pts (2nd)</t>
+          <t>'Man I Need' (2026 top 10, 43+ wks per Wikipedia); The Art of Loving</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -42208,7 +42208,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
+          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -42218,7 +42218,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>low confidence: far-out event</t>
+          <t>Good but the field reaches for it: let it come to you</t>
         </is>
       </c>
     </row>
@@ -42594,52 +42594,52 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Musician</t>
+          <t>NBA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bruno Mars</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Buckley</t>
         </is>
       </c>
       <c r="E17">
-        <f>'Musician'!M9</f>
+        <f>'NBA'!M7</f>
         <v/>
       </c>
       <c r="F17">
-        <f>'Musician'!N9</f>
+        <f>'NBA'!N7</f>
         <v/>
       </c>
       <c r="G17">
-        <f>'Musician'!O9</f>
+        <f>'NBA'!O7</f>
         <v/>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Grammy EV 7.3</t>
+          <t>Kalshi 8.5%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>'I Just Might' 3 wks #1 (Jan 2026); The Romantic</t>
+          <t>East; win total 52.5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
+          <t>KXNBA-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNBAEAST/KXNBAWEST-27 Kalshi mid</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -42647,11 +42647,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Good but the field reaches for it: let it come to you</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="n">
@@ -42659,29 +42655,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NBA</t>
+          <t>NHL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Florida Panthers</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Buckley</t>
+          <t>Todd</t>
         </is>
       </c>
       <c r="E18">
-        <f>'NBA'!M7</f>
+        <f>'NHL'!M7</f>
         <v/>
       </c>
       <c r="F18">
-        <f>'NBA'!N7</f>
+        <f>'NHL'!N7</f>
         <v/>
       </c>
       <c r="G18">
-        <f>'NBA'!O7</f>
+        <f>'NHL'!O7</f>
         <v/>
       </c>
       <c r="H18" t="n">
@@ -42689,12 +42685,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Kalshi 8.5%</t>
+          <t>Kalshi 10.5%</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>East; win total 52.5</t>
+          <t>East</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -42704,7 +42700,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>KXNBA-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNBAEAST/KXNBAWEST-27 Kalshi mid</t>
+          <t>KXNHL-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNHLEAST/KXNHLWEST-27 Kalshi mid</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -42720,52 +42716,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NHL</t>
+          <t>Golf</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Florida Panthers</t>
+          <t>Scottie Scheffler</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Todd</t>
+          <t>Wu</t>
         </is>
       </c>
       <c r="E19">
-        <f>'NHL'!M7</f>
+        <f>'Golf'!M5</f>
         <v/>
       </c>
       <c r="F19">
-        <f>'NHL'!N7</f>
+        <f>'Golf'!N5</f>
         <v/>
       </c>
       <c r="G19">
-        <f>'NHL'!O7</f>
+        <f>'Golf'!O5</f>
         <v/>
       </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Kalshi 10.5%</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>OWGR 1 (2026-10-08)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>KXNHL-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNHLEAST/KXNHLWEST-27 Kalshi mid</t>
+          <t>OWGR rank from league standings pull (A); major-win probabilities = model (rank-weighted share of 4 majors)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -42781,47 +42772,52 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>NCAAF</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scottie Scheffler</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>Wu</t>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E20">
-        <f>'Golf'!M5</f>
+        <f>'NCAAF'!M6</f>
         <v/>
       </c>
       <c r="F20">
-        <f>'Golf'!N5</f>
+        <f>'NCAAF'!N6</f>
         <v/>
       </c>
       <c r="G20">
-        <f>'Golf'!O5</f>
+        <f>'NCAAF'!O6</f>
         <v/>
       </c>
       <c r="H20" t="n">
         <v>1</v>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Kalshi 13.5%</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>OWGR 1 (2026-10-08)</t>
+          <t>AP #1, 4-0, SEC</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>OWGR rank from league standings pull (A); major-win probabilities = model (rank-weighted share of 4 majors)</t>
+          <t>KXNCAAF-27 exchange mid-price, pulled 2026-10-08</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -42837,12 +42833,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NCAAF</t>
+          <t>NBA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -42851,28 +42847,28 @@
         </is>
       </c>
       <c r="E21">
-        <f>'NCAAF'!M6</f>
+        <f>'NBA'!M8</f>
         <v/>
       </c>
       <c r="F21">
-        <f>'NCAAF'!N6</f>
+        <f>'NBA'!N8</f>
         <v/>
       </c>
       <c r="G21">
-        <f>'NCAAF'!O6</f>
+        <f>'NBA'!O8</f>
         <v/>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Kalshi 13.5%</t>
+          <t>Kalshi 12.5%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>AP #1, 4-0, SEC</t>
+          <t>East; win total 50.5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -42882,7 +42878,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>KXNCAAF-27 exchange mid-price, pulled 2026-10-08</t>
+          <t>KXNBA-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNBAEAST/KXNBAWEST-27 Kalshi mid</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -42898,12 +42894,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NBA</t>
+          <t>Musician</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Bruno Mars</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -42912,15 +42908,15 @@
         </is>
       </c>
       <c r="E22">
-        <f>'NBA'!M8</f>
+        <f>'Musician'!M9</f>
         <v/>
       </c>
       <c r="F22">
-        <f>'NBA'!N8</f>
+        <f>'Musician'!N9</f>
         <v/>
       </c>
       <c r="G22">
-        <f>'NBA'!O8</f>
+        <f>'Musician'!O9</f>
         <v/>
       </c>
       <c r="H22" t="n">
@@ -42928,22 +42924,22 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Kalshi 12.5%</t>
+          <t>Grammy EV 7.0 (raw 7.2, P(cap) 10%)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>East; win total 50.5</t>
+          <t>'I Just Might' 3 wks #1 (Jan 2026); The Romantic</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>KXNBA-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNBAEAST/KXNBAWEST-27 Kalshi mid</t>
+          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -42951,7 +42947,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Good but the field reaches for it: let it come to you</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="n">
@@ -45818,12 +45818,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Musician</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Harry Styles</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -45832,15 +45832,15 @@
         </is>
       </c>
       <c r="E70">
-        <f>'Country'!M9</f>
+        <f>'Musician'!M10</f>
         <v/>
       </c>
       <c r="F70">
-        <f>'Country'!N9</f>
+        <f>'Musician'!N10</f>
         <v/>
       </c>
       <c r="G70">
-        <f>'Country'!O9</f>
+        <f>'Musician'!O10</f>
         <v/>
       </c>
       <c r="H70" t="n">
@@ -45848,22 +45848,22 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>IMF WEO Apr-2025: 7.9%</t>
+          <t>Grammy EV 3.8 (raw 3.8, P(cap) 1%)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>LNG expansion</t>
+          <t>'Aperture' 1 wk #1 (Feb 2026); 'Kiss All the Time. Disco, Occasionally'</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
+          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -45871,7 +45871,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Good but the field reaches for it: let it come to you</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -45879,12 +45883,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Musician</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Harry Styles</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -45893,15 +45897,15 @@
         </is>
       </c>
       <c r="E71">
-        <f>'Musician'!M10</f>
+        <f>'Country'!M9</f>
         <v/>
       </c>
       <c r="F71">
-        <f>'Musician'!N10</f>
+        <f>'Country'!N9</f>
         <v/>
       </c>
       <c r="G71">
-        <f>'Musician'!O10</f>
+        <f>'Country'!O9</f>
         <v/>
       </c>
       <c r="H71" t="n">
@@ -45909,22 +45913,22 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Grammy EV 3.7</t>
+          <t>IMF WEO Apr-2025: 7.9%</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>'Aperture' 1 wk #1 (Feb 2026); 'Kiss All the Time. Disco, Occasionally'</t>
+          <t>LNG expansion</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
+          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -45932,11 +45936,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>Good but the field reaches for it: let it come to you</t>
-        </is>
-      </c>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -49705,29 +49705,29 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Musician</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Rosalía</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>Tim</t>
         </is>
       </c>
       <c r="E134">
-        <f>'Musician'!M12</f>
+        <f>'MLS'!M15</f>
         <v/>
       </c>
       <c r="F134">
-        <f>'Musician'!N12</f>
+        <f>'MLS'!N15</f>
         <v/>
       </c>
       <c r="G134">
-        <f>'Musician'!O12</f>
+        <f>'MLS'!O15</f>
         <v/>
       </c>
       <c r="H134" t="n">
@@ -49735,12 +49735,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Grammy EV 7.0</t>
+          <t>2026 Cup: Kalshi 2.5%</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Lux (Grammy-driven pick; small Hot 100 profile)</t>
+          <t>2026: 43 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -49750,7 +49750,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
+          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -49760,7 +49760,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>Overpriced by the field on award buzz: skip</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -49770,42 +49770,37 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Actor</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Charlotte FC</t>
-        </is>
-      </c>
-      <c r="D135" s="11" t="inlineStr">
-        <is>
-          <t>Tim</t>
+          <t>Matt Berry</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E135">
-        <f>'MLS'!M15</f>
+        <f>'Actor'!M12</f>
         <v/>
       </c>
       <c r="F135">
-        <f>'MLS'!N15</f>
+        <f>'Actor'!N12</f>
         <v/>
       </c>
       <c r="G135">
-        <f>'MLS'!O15</f>
+        <f>'Actor'!O12</f>
         <v/>
       </c>
       <c r="H135" t="n">
         <v>3</v>
       </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>2026 Cup: Kalshi 2.5%</t>
-        </is>
-      </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>2026: 43 pts (as of 10-08; season ends Nov 7)</t>
+          <t>Sonic the Hedgehog 4 (Mar 19); A Minecraft Movie Squared (Jul 23)</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -49815,7 +49810,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -49825,7 +49820,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>low confidence: far-out event</t>
+          <t>late filler</t>
         </is>
       </c>
     </row>
@@ -49835,37 +49830,42 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Actor</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Matt Berry</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>Mitchell</t>
         </is>
       </c>
       <c r="E136">
-        <f>'Actor'!M12</f>
+        <f>'MLS'!M16</f>
         <v/>
       </c>
       <c r="F136">
-        <f>'Actor'!N12</f>
+        <f>'MLS'!N16</f>
         <v/>
       </c>
       <c r="G136">
-        <f>'Actor'!O12</f>
+        <f>'MLS'!O16</f>
         <v/>
       </c>
       <c r="H136" t="n">
         <v>3</v>
       </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2026 Cup: Kalshi 3.5%</t>
+        </is>
+      </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Sonic the Hedgehog 4 (Mar 19); A Minecraft Movie Squared (Jul 23)</t>
+          <t>2026: 39 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -49875,7 +49875,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -49885,7 +49885,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>late filler</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -49895,42 +49895,37 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
-        </is>
-      </c>
-      <c r="D137" s="11" t="inlineStr">
-        <is>
-          <t>Mitchell</t>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E137">
-        <f>'MLS'!M16</f>
+        <f>'MLB'!M13</f>
         <v/>
       </c>
       <c r="F137">
-        <f>'MLS'!N16</f>
+        <f>'MLB'!N13</f>
         <v/>
       </c>
       <c r="G137">
-        <f>'MLS'!O16</f>
+        <f>'MLB'!O13</f>
         <v/>
       </c>
       <c r="H137" t="n">
         <v>3</v>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>2026 Cup: Kalshi 3.5%</t>
-        </is>
-      </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>2026: 39 pts (as of 10-08; season ends Nov 7)</t>
+          <t>2026: 87-75 (.5370)</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -49940,7 +49935,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
+          <t>2026 win% from league standings (A); title prob = model estimate — no 2027 World Series odds posted</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -49960,12 +49955,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>Actor</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Andrew Scott</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -49974,15 +49969,15 @@
         </is>
       </c>
       <c r="E138">
-        <f>'MLB'!M13</f>
+        <f>'Actor'!M13</f>
         <v/>
       </c>
       <c r="F138">
-        <f>'MLB'!N13</f>
+        <f>'Actor'!N13</f>
         <v/>
       </c>
       <c r="G138">
-        <f>'MLB'!O13</f>
+        <f>'Actor'!O13</f>
         <v/>
       </c>
       <c r="H138" t="n">
@@ -49990,7 +49985,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>2026: 87-75 (.5370)</t>
+          <t>Margie Claus (Nov 12); A Place in Hell (Apr 23)</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -50000,7 +49995,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026 win% from league standings (A); title prob = model estimate — no 2027 World Series odds posted</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -50010,7 +50005,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>low confidence: far-out event</t>
+          <t>Overpriced by the field on award buzz: skip</t>
         </is>
       </c>
     </row>
@@ -50020,37 +50015,42 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Actor</t>
+          <t>NASCAR</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Andrew Scott</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Shane van Gisbergen</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>Mitchell</t>
         </is>
       </c>
       <c r="E139">
-        <f>'Actor'!M13</f>
+        <f>'NASCAR'!M14</f>
         <v/>
       </c>
       <c r="F139">
-        <f>'Actor'!N13</f>
+        <f>'NASCAR'!N14</f>
         <v/>
       </c>
       <c r="G139">
-        <f>'Actor'!O13</f>
+        <f>'NASCAR'!O14</f>
         <v/>
       </c>
       <c r="H139" t="n">
         <v>3</v>
       </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2026 title: Kalshi 0.5%</t>
+        </is>
+      </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Margie Claus (Nov 12); A Place in Hell (Apr 23)</t>
+          <t>2026 Cup Series</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -50060,7 +50060,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -50070,7 +50070,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>Overpriced by the field on award buzz: skip</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -50085,24 +50085,24 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Shane van Gisbergen</t>
-        </is>
-      </c>
-      <c r="D140" s="11" t="inlineStr">
-        <is>
-          <t>Mitchell</t>
+          <t>Michael McDowell</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E140">
-        <f>'NASCAR'!M14</f>
+        <f>'NASCAR'!M15</f>
         <v/>
       </c>
       <c r="F140">
-        <f>'NASCAR'!N14</f>
+        <f>'NASCAR'!N15</f>
         <v/>
       </c>
       <c r="G140">
-        <f>'NASCAR'!O14</f>
+        <f>'NASCAR'!O15</f>
         <v/>
       </c>
       <c r="H140" t="n">
@@ -50150,7 +50150,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Michael McDowell</t>
+          <t>Ty Gibbs</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -50159,15 +50159,15 @@
         </is>
       </c>
       <c r="E141">
-        <f>'NASCAR'!M15</f>
+        <f>'NASCAR'!M16</f>
         <v/>
       </c>
       <c r="F141">
-        <f>'NASCAR'!N15</f>
+        <f>'NASCAR'!N16</f>
         <v/>
       </c>
       <c r="G141">
-        <f>'NASCAR'!O15</f>
+        <f>'NASCAR'!O16</f>
         <v/>
       </c>
       <c r="H141" t="n">
@@ -50215,7 +50215,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ty Gibbs</t>
+          <t>AJ Allmendinger</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -50224,15 +50224,15 @@
         </is>
       </c>
       <c r="E142">
-        <f>'NASCAR'!M16</f>
+        <f>'NASCAR'!M17</f>
         <v/>
       </c>
       <c r="F142">
-        <f>'NASCAR'!N16</f>
+        <f>'NASCAR'!N17</f>
         <v/>
       </c>
       <c r="G142">
-        <f>'NASCAR'!O16</f>
+        <f>'NASCAR'!O17</f>
         <v/>
       </c>
       <c r="H142" t="n">
@@ -50280,7 +50280,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AJ Allmendinger</t>
+          <t>Alex Bowman</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -50289,19 +50289,19 @@
         </is>
       </c>
       <c r="E143">
-        <f>'NASCAR'!M17</f>
+        <f>'NASCAR'!M18</f>
         <v/>
       </c>
       <c r="F143">
-        <f>'NASCAR'!N17</f>
+        <f>'NASCAR'!N18</f>
         <v/>
       </c>
       <c r="G143">
-        <f>'NASCAR'!O17</f>
+        <f>'NASCAR'!O18</f>
         <v/>
       </c>
       <c r="H143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -50345,7 +50345,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Alex Bowman</t>
+          <t>Riley Herbst</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -50354,15 +50354,15 @@
         </is>
       </c>
       <c r="E144">
-        <f>'NASCAR'!M18</f>
+        <f>'NASCAR'!M19</f>
         <v/>
       </c>
       <c r="F144">
-        <f>'NASCAR'!N18</f>
+        <f>'NASCAR'!N19</f>
         <v/>
       </c>
       <c r="G144">
-        <f>'NASCAR'!O18</f>
+        <f>'NASCAR'!O19</f>
         <v/>
       </c>
       <c r="H144" t="n">
@@ -50410,24 +50410,24 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Riley Herbst</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Ross Chastain</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>Buckley</t>
         </is>
       </c>
       <c r="E145">
-        <f>'NASCAR'!M19</f>
+        <f>'NASCAR'!M20</f>
         <v/>
       </c>
       <c r="F145">
-        <f>'NASCAR'!N19</f>
+        <f>'NASCAR'!N20</f>
         <v/>
       </c>
       <c r="G145">
-        <f>'NASCAR'!O19</f>
+        <f>'NASCAR'!O20</f>
         <v/>
       </c>
       <c r="H145" t="n">
@@ -50475,24 +50475,24 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ross Chastain</t>
-        </is>
-      </c>
-      <c r="D146" s="11" t="inlineStr">
-        <is>
-          <t>Buckley</t>
+          <t>Todd Gilliland</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E146">
-        <f>'NASCAR'!M20</f>
+        <f>'NASCAR'!M21</f>
         <v/>
       </c>
       <c r="F146">
-        <f>'NASCAR'!N20</f>
+        <f>'NASCAR'!N21</f>
         <v/>
       </c>
       <c r="G146">
-        <f>'NASCAR'!O20</f>
+        <f>'NASCAR'!O21</f>
         <v/>
       </c>
       <c r="H146" t="n">
@@ -50540,7 +50540,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Todd Gilliland</t>
+          <t>Ryan Preece</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -50549,15 +50549,15 @@
         </is>
       </c>
       <c r="E147">
-        <f>'NASCAR'!M21</f>
+        <f>'NASCAR'!M22</f>
         <v/>
       </c>
       <c r="F147">
-        <f>'NASCAR'!N21</f>
+        <f>'NASCAR'!N22</f>
         <v/>
       </c>
       <c r="G147">
-        <f>'NASCAR'!O21</f>
+        <f>'NASCAR'!O22</f>
         <v/>
       </c>
       <c r="H147" t="n">
@@ -50605,24 +50605,24 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Ryan Preece</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Bubba Wallace</t>
+        </is>
+      </c>
+      <c r="D148" s="11" t="inlineStr">
+        <is>
+          <t>Tim</t>
         </is>
       </c>
       <c r="E148">
-        <f>'NASCAR'!M22</f>
+        <f>'NASCAR'!M23</f>
         <v/>
       </c>
       <c r="F148">
-        <f>'NASCAR'!N22</f>
+        <f>'NASCAR'!N23</f>
         <v/>
       </c>
       <c r="G148">
-        <f>'NASCAR'!O22</f>
+        <f>'NASCAR'!O23</f>
         <v/>
       </c>
       <c r="H148" t="n">
@@ -50670,24 +50670,24 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bubba Wallace</t>
-        </is>
-      </c>
-      <c r="D149" s="11" t="inlineStr">
-        <is>
-          <t>Tim</t>
+          <t>Zane Smith</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E149">
-        <f>'NASCAR'!M23</f>
+        <f>'NASCAR'!M24</f>
         <v/>
       </c>
       <c r="F149">
-        <f>'NASCAR'!N23</f>
+        <f>'NASCAR'!N24</f>
         <v/>
       </c>
       <c r="G149">
-        <f>'NASCAR'!O23</f>
+        <f>'NASCAR'!O24</f>
         <v/>
       </c>
       <c r="H149" t="n">
@@ -50735,7 +50735,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Zane Smith</t>
+          <t>Noah Gragson</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -50744,15 +50744,15 @@
         </is>
       </c>
       <c r="E150">
-        <f>'NASCAR'!M24</f>
+        <f>'NASCAR'!M25</f>
         <v/>
       </c>
       <c r="F150">
-        <f>'NASCAR'!N24</f>
+        <f>'NASCAR'!N25</f>
         <v/>
       </c>
       <c r="G150">
-        <f>'NASCAR'!O24</f>
+        <f>'NASCAR'!O25</f>
         <v/>
       </c>
       <c r="H150" t="n">
@@ -50800,7 +50800,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Noah Gragson</t>
+          <t>Austin Cindric</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -50809,15 +50809,15 @@
         </is>
       </c>
       <c r="E151">
-        <f>'NASCAR'!M25</f>
+        <f>'NASCAR'!M26</f>
         <v/>
       </c>
       <c r="F151">
-        <f>'NASCAR'!N25</f>
+        <f>'NASCAR'!N26</f>
         <v/>
       </c>
       <c r="G151">
-        <f>'NASCAR'!O25</f>
+        <f>'NASCAR'!O26</f>
         <v/>
       </c>
       <c r="H151" t="n">
@@ -50865,24 +50865,24 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Austin Cindric</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Daniel Suarez</t>
+        </is>
+      </c>
+      <c r="D152" s="11" t="inlineStr">
+        <is>
+          <t>Shep</t>
         </is>
       </c>
       <c r="E152">
-        <f>'NASCAR'!M26</f>
+        <f>'NASCAR'!M27</f>
         <v/>
       </c>
       <c r="F152">
-        <f>'NASCAR'!N26</f>
+        <f>'NASCAR'!N27</f>
         <v/>
       </c>
       <c r="G152">
-        <f>'NASCAR'!O26</f>
+        <f>'NASCAR'!O27</f>
         <v/>
       </c>
       <c r="H152" t="n">
@@ -50930,24 +50930,24 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Daniel Suarez</t>
-        </is>
-      </c>
-      <c r="D153" s="11" t="inlineStr">
-        <is>
-          <t>Shep</t>
+          <t>Carson Hocevar</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E153">
-        <f>'NASCAR'!M27</f>
+        <f>'NASCAR'!M28</f>
         <v/>
       </c>
       <c r="F153">
-        <f>'NASCAR'!N27</f>
+        <f>'NASCAR'!N28</f>
         <v/>
       </c>
       <c r="G153">
-        <f>'NASCAR'!O27</f>
+        <f>'NASCAR'!O28</f>
         <v/>
       </c>
       <c r="H153" t="n">
@@ -50990,42 +50990,42 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NASCAR</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Carson Hocevar</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Seattle Sounders FC</t>
+        </is>
+      </c>
+      <c r="D154" s="11" t="inlineStr">
+        <is>
+          <t>Jamzee</t>
         </is>
       </c>
       <c r="E154">
-        <f>'NASCAR'!M28</f>
+        <f>'MLS'!M17</f>
         <v/>
       </c>
       <c r="F154">
-        <f>'NASCAR'!N28</f>
+        <f>'MLS'!N17</f>
         <v/>
       </c>
       <c r="G154">
-        <f>'NASCAR'!O28</f>
+        <f>'MLS'!O17</f>
         <v/>
       </c>
       <c r="H154" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026 title: Kalshi 0.5%</t>
+          <t>2026 Cup: Kalshi 1.5%</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>2026 Cup Series</t>
+          <t>2026: 38 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -51035,7 +51035,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>User-supplied final Cup standings 2021-2026(proj.), recency-weighted (decay 0.65/yr, nascar_model.py) for drivers in the table; others = field prior blended with 2026 Kalshi title price (shrunk). No 2027 market exists.</t>
+          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -51055,42 +51055,37 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Actress</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Seattle Sounders FC</t>
-        </is>
-      </c>
-      <c r="D155" s="11" t="inlineStr">
-        <is>
-          <t>Jamzee</t>
+          <t>Amy Adams</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E155">
-        <f>'MLS'!M17</f>
+        <f>'Actress'!M12</f>
         <v/>
       </c>
       <c r="F155">
-        <f>'MLS'!N17</f>
+        <f>'Actress'!N12</f>
         <v/>
       </c>
       <c r="G155">
-        <f>'MLS'!O17</f>
+        <f>'Actress'!O12</f>
         <v/>
       </c>
       <c r="H155" t="n">
         <v>3</v>
       </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>2026 Cup: Kalshi 1.5%</t>
-        </is>
-      </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>2026: 38 pts (as of 10-08; season ends Nov 7)</t>
+          <t>Starfighter (May 28)</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -51100,7 +51095,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -51110,7 +51105,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>low confidence: far-out event</t>
+          <t>late filler</t>
         </is>
       </c>
     </row>
@@ -51120,37 +51115,42 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Actress</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Amy Adams</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="D156" s="11" t="inlineStr">
+        <is>
+          <t>Molmen</t>
         </is>
       </c>
       <c r="E156">
-        <f>'Actress'!M12</f>
+        <f>'MLS'!M18</f>
         <v/>
       </c>
       <c r="F156">
-        <f>'Actress'!N12</f>
+        <f>'MLS'!N18</f>
         <v/>
       </c>
       <c r="G156">
-        <f>'Actress'!O12</f>
+        <f>'MLS'!O18</f>
         <v/>
       </c>
       <c r="H156" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>2026 Cup: Kalshi 1.5%</t>
+        </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Starfighter (May 28)</t>
+          <t>2026: 36 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -51160,7 +51160,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -51170,7 +51170,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>late filler</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -51180,42 +51180,37 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Golf</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
-        </is>
-      </c>
-      <c r="D157" s="11" t="inlineStr">
-        <is>
-          <t>Molmen</t>
+          <t>Chris Gotterup</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E157">
-        <f>'MLS'!M18</f>
+        <f>'Golf'!M12</f>
         <v/>
       </c>
       <c r="F157">
-        <f>'MLS'!N18</f>
+        <f>'Golf'!N12</f>
         <v/>
       </c>
       <c r="G157">
-        <f>'MLS'!O18</f>
+        <f>'Golf'!O12</f>
         <v/>
       </c>
       <c r="H157" t="n">
-        <v>4</v>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>2026 Cup: Kalshi 1.5%</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>2026: 36 pts (as of 10-08; season ends Nov 7)</t>
+          <t>OWGR 8 (2026-10-08)</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -51225,7 +51220,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
+          <t>OWGR rank from league standings pull (A); major-win probabilities = model (rank-weighted share of 4 majors)</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -51233,11 +51228,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>low confidence: far-out event</t>
-        </is>
-      </c>
+      <c r="N157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -51245,12 +51236,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>Actor</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Chris Gotterup</t>
+          <t>Shameik Moore</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -51259,15 +51250,15 @@
         </is>
       </c>
       <c r="E158">
-        <f>'Golf'!M12</f>
+        <f>'Actor'!M14</f>
         <v/>
       </c>
       <c r="F158">
-        <f>'Golf'!N12</f>
+        <f>'Actor'!N14</f>
         <v/>
       </c>
       <c r="G158">
-        <f>'Golf'!O12</f>
+        <f>'Actor'!O14</f>
         <v/>
       </c>
       <c r="H158" t="n">
@@ -51275,7 +51266,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>OWGR 8 (2026-10-08)</t>
+          <t>Spider-Man: Beyond the Spider-Verse (Jun 18)</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -51285,7 +51276,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>OWGR rank from league standings pull (A); major-win probabilities = model (rank-weighted share of 4 majors)</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -51293,7 +51284,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N158" t="inlineStr"/>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>late filler</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -51306,7 +51301,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Shameik Moore</t>
+          <t>Jake Johnson</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -51315,15 +51310,15 @@
         </is>
       </c>
       <c r="E159">
-        <f>'Actor'!M14</f>
+        <f>'Actor'!M15</f>
         <v/>
       </c>
       <c r="F159">
-        <f>'Actor'!N14</f>
+        <f>'Actor'!N15</f>
         <v/>
       </c>
       <c r="G159">
-        <f>'Actor'!O14</f>
+        <f>'Actor'!O15</f>
         <v/>
       </c>
       <c r="H159" t="n">
@@ -51361,12 +51356,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Actor</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Jake Johnson</t>
+          <t>Mirra Andreeva</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -51375,15 +51370,15 @@
         </is>
       </c>
       <c r="E160">
-        <f>'Actor'!M15</f>
+        <f>'Tennis'!M13</f>
         <v/>
       </c>
       <c r="F160">
-        <f>'Actor'!N15</f>
+        <f>'Tennis'!N13</f>
         <v/>
       </c>
       <c r="G160">
-        <f>'Actor'!O15</f>
+        <f>'Tennis'!O13</f>
         <v/>
       </c>
       <c r="H160" t="n">
@@ -51391,7 +51386,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Spider-Man: Beyond the Spider-Verse (Jun 18)</t>
+          <t>WTA 5 (2026-10-08)</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -51401,7 +51396,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>ATP rank from league standings pull (A) / WTA via Olympics.com Oct 5; AO odds VegasInsider/Johnnybet Oct 2026; probabilities = agent estimates</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -51409,11 +51404,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N160" t="inlineStr">
-        <is>
-          <t>late filler</t>
-        </is>
-      </c>
+      <c r="N160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -51421,47 +51412,52 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>NBA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Mirra Andreeva</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="D161" s="11" t="inlineStr">
+        <is>
+          <t>Tim</t>
         </is>
       </c>
       <c r="E161">
-        <f>'Tennis'!M13</f>
+        <f>'NBA'!M12</f>
         <v/>
       </c>
       <c r="F161">
-        <f>'Tennis'!N13</f>
+        <f>'NBA'!N12</f>
         <v/>
       </c>
       <c r="G161">
-        <f>'Tennis'!O13</f>
+        <f>'NBA'!O12</f>
         <v/>
       </c>
       <c r="H161" t="n">
         <v>3</v>
       </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Kalshi 2.5%</t>
+        </is>
+      </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>WTA 5 (2026-10-08)</t>
+          <t>West; win total 49.5</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>ATP rank from league standings pull (A) / WTA via Olympics.com Oct 5; AO odds VegasInsider/Johnnybet Oct 2026; probabilities = agent estimates</t>
+          <t>KXNBA-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNBAEAST/KXNBAWEST-27 Kalshi mid</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -51477,52 +51473,47 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>NBA</t>
+          <t>Actress</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="D162" s="11" t="inlineStr">
-        <is>
-          <t>Tim</t>
+          <t>Mia Goth</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E162">
-        <f>'NBA'!M12</f>
+        <f>'Actress'!M13</f>
         <v/>
       </c>
       <c r="F162">
-        <f>'NBA'!N12</f>
+        <f>'Actress'!N13</f>
         <v/>
       </c>
       <c r="G162">
-        <f>'NBA'!O12</f>
+        <f>'Actress'!O13</f>
         <v/>
       </c>
       <c r="H162" t="n">
         <v>3</v>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Kalshi 2.5%</t>
-        </is>
-      </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>West; win total 49.5</t>
+          <t>Starfighter (May 28)</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>KXNBA-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNBAEAST/KXNBAWEST-27 Kalshi mid</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -51530,7 +51521,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>late filler</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -51538,12 +51533,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Actress</t>
+          <t>Actor</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Mia Goth</t>
+          <t>Jason Schwartzman</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -51552,15 +51547,15 @@
         </is>
       </c>
       <c r="E163">
-        <f>'Actress'!M13</f>
+        <f>'Actor'!M16</f>
         <v/>
       </c>
       <c r="F163">
-        <f>'Actress'!N13</f>
+        <f>'Actor'!N16</f>
         <v/>
       </c>
       <c r="G163">
-        <f>'Actress'!O13</f>
+        <f>'Actor'!O16</f>
         <v/>
       </c>
       <c r="H163" t="n">
@@ -51568,7 +51563,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Starfighter (May 28)</t>
+          <t>Spider-Man: Beyond the Spider-Verse (Jun 18)</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -51603,7 +51598,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Jason Schwartzman</t>
+          <t>John Mulaney</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -51612,15 +51607,15 @@
         </is>
       </c>
       <c r="E164">
-        <f>'Actor'!M16</f>
+        <f>'Actor'!M17</f>
         <v/>
       </c>
       <c r="F164">
-        <f>'Actor'!N16</f>
+        <f>'Actor'!N17</f>
         <v/>
       </c>
       <c r="G164">
-        <f>'Actor'!O16</f>
+        <f>'Actor'!O17</f>
         <v/>
       </c>
       <c r="H164" t="n">
@@ -51658,37 +51653,42 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Actor</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>John Mulaney</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Orlando City SC</t>
+        </is>
+      </c>
+      <c r="D165" s="11" t="inlineStr">
+        <is>
+          <t>Shep</t>
         </is>
       </c>
       <c r="E165">
-        <f>'Actor'!M17</f>
+        <f>'MLS'!M19</f>
         <v/>
       </c>
       <c r="F165">
-        <f>'Actor'!N17</f>
+        <f>'MLS'!N19</f>
         <v/>
       </c>
       <c r="G165">
-        <f>'Actor'!O17</f>
+        <f>'MLS'!O19</f>
         <v/>
       </c>
       <c r="H165" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>2026 Cup: Kalshi 0.5%</t>
+        </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Spider-Man: Beyond the Spider-Verse (Jun 18)</t>
+          <t>2026: 34 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -51698,7 +51698,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -51708,7 +51708,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>late filler</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -51718,42 +51718,37 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Actor</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Orlando City SC</t>
-        </is>
-      </c>
-      <c r="D166" s="11" t="inlineStr">
-        <is>
-          <t>Shep</t>
+          <t>Karan Soni</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E166">
-        <f>'MLS'!M19</f>
+        <f>'Actor'!M18</f>
         <v/>
       </c>
       <c r="F166">
-        <f>'MLS'!N19</f>
+        <f>'Actor'!N18</f>
         <v/>
       </c>
       <c r="G166">
-        <f>'MLS'!O19</f>
+        <f>'Actor'!O18</f>
         <v/>
       </c>
       <c r="H166" t="n">
         <v>4</v>
       </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>2026 Cup: Kalshi 0.5%</t>
-        </is>
-      </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>2026: 34 pts (as of 10-08; season ends Nov 7)</t>
+          <t>Spider-Man: Beyond the Spider-Verse (Jun 18)</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -51763,7 +51758,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -51773,7 +51768,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>low confidence: far-out event</t>
+          <t>late filler</t>
         </is>
       </c>
     </row>
@@ -51783,12 +51778,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Actor</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Karan Soni</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -51797,23 +51792,28 @@
         </is>
       </c>
       <c r="E167">
-        <f>'Actor'!M18</f>
+        <f>'MLS'!M20</f>
         <v/>
       </c>
       <c r="F167">
-        <f>'Actor'!N18</f>
+        <f>'MLS'!N20</f>
         <v/>
       </c>
       <c r="G167">
-        <f>'Actor'!O18</f>
+        <f>'MLS'!O20</f>
         <v/>
       </c>
       <c r="H167" t="n">
         <v>4</v>
       </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>2026 Cup: Kalshi 0.5%</t>
+        </is>
+      </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Spider-Man: Beyond the Spider-Verse (Jun 18)</t>
+          <t>2026: 36 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -51823,7 +51823,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -51833,7 +51833,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>late filler</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -51843,12 +51843,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Actor</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Daniel Kaluuya</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -51857,28 +51857,23 @@
         </is>
       </c>
       <c r="E168">
-        <f>'MLS'!M20</f>
+        <f>'Actor'!M19</f>
         <v/>
       </c>
       <c r="F168">
-        <f>'MLS'!N20</f>
+        <f>'Actor'!N19</f>
         <v/>
       </c>
       <c r="G168">
-        <f>'MLS'!O20</f>
+        <f>'Actor'!O19</f>
         <v/>
       </c>
       <c r="H168" t="n">
         <v>4</v>
       </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>2026 Cup: Kalshi 0.5%</t>
-        </is>
-      </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>2026: 36 pts (as of 10-08; season ends Nov 7)</t>
+          <t>Spider-Man: Beyond the Spider-Verse (Jun 18)</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -51888,7 +51883,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -51898,7 +51893,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>low confidence: far-out event</t>
+          <t>late filler</t>
         </is>
       </c>
     </row>
@@ -51913,7 +51908,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Daniel Kaluuya</t>
+          <t>Oscar Isaac</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -51922,15 +51917,15 @@
         </is>
       </c>
       <c r="E169">
-        <f>'Actor'!M19</f>
+        <f>'Actor'!M20</f>
         <v/>
       </c>
       <c r="F169">
-        <f>'Actor'!N19</f>
+        <f>'Actor'!N20</f>
         <v/>
       </c>
       <c r="G169">
-        <f>'Actor'!O19</f>
+        <f>'Actor'!O20</f>
         <v/>
       </c>
       <c r="H169" t="n">
@@ -51973,7 +51968,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Oscar Isaac</t>
+          <t>Nicolas Cage</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -51982,15 +51977,15 @@
         </is>
       </c>
       <c r="E170">
-        <f>'Actor'!M20</f>
+        <f>'Actor'!M21</f>
         <v/>
       </c>
       <c r="F170">
-        <f>'Actor'!N20</f>
+        <f>'Actor'!N21</f>
         <v/>
       </c>
       <c r="G170">
-        <f>'Actor'!O20</f>
+        <f>'Actor'!O21</f>
         <v/>
       </c>
       <c r="H170" t="n">
@@ -52033,7 +52028,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Nicolas Cage</t>
+          <t>Mahershala Ali</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -52042,15 +52037,15 @@
         </is>
       </c>
       <c r="E171">
-        <f>'Actor'!M21</f>
+        <f>'Actor'!M22</f>
         <v/>
       </c>
       <c r="F171">
-        <f>'Actor'!N21</f>
+        <f>'Actor'!N22</f>
         <v/>
       </c>
       <c r="G171">
-        <f>'Actor'!O21</f>
+        <f>'Actor'!O22</f>
         <v/>
       </c>
       <c r="H171" t="n">
@@ -52088,37 +52083,42 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Actor</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Mahershala Ali</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>New York Red Bulls</t>
+        </is>
+      </c>
+      <c r="D172" s="11" t="inlineStr">
+        <is>
+          <t>Todd</t>
         </is>
       </c>
       <c r="E172">
-        <f>'Actor'!M22</f>
+        <f>'MLS'!M21</f>
         <v/>
       </c>
       <c r="F172">
-        <f>'Actor'!N22</f>
+        <f>'MLS'!N21</f>
         <v/>
       </c>
       <c r="G172">
-        <f>'Actor'!O22</f>
+        <f>'MLS'!O21</f>
         <v/>
       </c>
       <c r="H172" t="n">
         <v>4</v>
       </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>2026 Cup: Kalshi 0.5%</t>
+        </is>
+      </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Spider-Man: Beyond the Spider-Verse (Jun 18)</t>
+          <t>2026: 33 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -52128,7 +52128,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -52138,7 +52138,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>late filler</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -52148,42 +52148,42 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Musician</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>New York Red Bulls</t>
+          <t>BTS</t>
         </is>
       </c>
       <c r="D173" s="11" t="inlineStr">
         <is>
-          <t>Todd</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="E173">
-        <f>'MLS'!M21</f>
+        <f>'Musician'!M12</f>
         <v/>
       </c>
       <c r="F173">
-        <f>'MLS'!N21</f>
+        <f>'Musician'!N12</f>
         <v/>
       </c>
       <c r="G173">
-        <f>'MLS'!O21</f>
+        <f>'Musician'!O12</f>
         <v/>
       </c>
       <c r="H173" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2026 Cup: Kalshi 0.5%</t>
+          <t>Grammy EV 2.6</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>2026: 33 pts (as of 10-08; season ends Nov 7)</t>
+          <t>Arirang (2026) #1 on the Billboard 200; 'Swim' #1 (Apr 2026); world tour</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -52193,7 +52193,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
+          <t>2027 Hot 100 baseline = my estimate; Grammy: estimate (C)</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -52203,7 +52203,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>low confidence: far-out event</t>
+          <t>late filler</t>
         </is>
       </c>
     </row>
@@ -52213,42 +52213,42 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Musician</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>BTS</t>
-        </is>
-      </c>
-      <c r="D174" s="11" t="inlineStr">
-        <is>
-          <t>Theo</t>
+          <t>New York City FC</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E174">
-        <f>'Musician'!M13</f>
+        <f>'MLS'!M22</f>
         <v/>
       </c>
       <c r="F174">
-        <f>'Musician'!N13</f>
+        <f>'MLS'!N22</f>
         <v/>
       </c>
       <c r="G174">
-        <f>'Musician'!O13</f>
+        <f>'MLS'!O22</f>
         <v/>
       </c>
       <c r="H174" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Grammy EV 2.6</t>
+          <t>2026 Cup: Kalshi 0.5%</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Arirang (2026) #1 on the Billboard 200; 'Swim' #1 (Apr 2026); world tour</t>
+          <t>2026: 33 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -52258,7 +52258,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2027 Hot 100 baseline = my estimate; Grammy: estimate (C)</t>
+          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -52268,7 +52268,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>late filler</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -52278,52 +52278,52 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>NHL</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>New York City FC</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Tampa Bay Lightning</t>
+        </is>
+      </c>
+      <c r="D175" s="11" t="inlineStr">
+        <is>
+          <t>Fryar</t>
         </is>
       </c>
       <c r="E175">
-        <f>'MLS'!M22</f>
+        <f>'NHL'!M12</f>
         <v/>
       </c>
       <c r="F175">
-        <f>'MLS'!N22</f>
+        <f>'NHL'!N12</f>
         <v/>
       </c>
       <c r="G175">
-        <f>'MLS'!O22</f>
+        <f>'NHL'!O12</f>
         <v/>
       </c>
       <c r="H175" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2026 Cup: Kalshi 0.5%</t>
+          <t>Kalshi 5.5%</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>2026: 33 pts (as of 10-08; season ends Nov 7)</t>
+          <t>East</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
+          <t>KXNHL-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNHLEAST/KXNHLWEST-27 Kalshi mid</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -52331,11 +52331,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>low confidence: far-out event</t>
-        </is>
-      </c>
+      <c r="N175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -52343,52 +52339,52 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>NHL</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Tampa Bay Lightning</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="D176" s="11" t="inlineStr">
         <is>
-          <t>Fryar</t>
+          <t>Korch</t>
         </is>
       </c>
       <c r="E176">
-        <f>'NHL'!M12</f>
+        <f>'MLS'!M23</f>
         <v/>
       </c>
       <c r="F176">
-        <f>'NHL'!N12</f>
+        <f>'MLS'!N23</f>
         <v/>
       </c>
       <c r="G176">
-        <f>'NHL'!O12</f>
+        <f>'MLS'!O23</f>
         <v/>
       </c>
       <c r="H176" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Kalshi 5.5%</t>
+          <t>2026 Cup: Kalshi 0.5%</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>2026: 33 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>KXNHL-27 exchange mid-price, pulled 2026-10-08; p(final)=KXNHLEAST/KXNHLWEST-27 Kalshi mid</t>
+          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -52396,7 +52392,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>low confidence: far-out event</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -52409,24 +52409,24 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>San Diego FC</t>
         </is>
       </c>
       <c r="D177" s="11" t="inlineStr">
         <is>
-          <t>Korch</t>
+          <t>Jens</t>
         </is>
       </c>
       <c r="E177">
-        <f>'MLS'!M23</f>
+        <f>'MLS'!M24</f>
         <v/>
       </c>
       <c r="F177">
-        <f>'MLS'!N23</f>
+        <f>'MLS'!N24</f>
         <v/>
       </c>
       <c r="G177">
-        <f>'MLS'!O23</f>
+        <f>'MLS'!O24</f>
         <v/>
       </c>
       <c r="H177" t="n">
@@ -52439,7 +52439,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>2026: 33 pts (as of 10-08; season ends Nov 7)</t>
+          <t>2026: 32 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -52474,24 +52474,24 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>San Diego FC</t>
-        </is>
-      </c>
-      <c r="D178" s="11" t="inlineStr">
-        <is>
-          <t>Jens</t>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E178">
-        <f>'MLS'!M24</f>
+        <f>'MLS'!M25</f>
         <v/>
       </c>
       <c r="F178">
-        <f>'MLS'!N24</f>
+        <f>'MLS'!N25</f>
         <v/>
       </c>
       <c r="G178">
-        <f>'MLS'!O24</f>
+        <f>'MLS'!O25</f>
         <v/>
       </c>
       <c r="H178" t="n">
@@ -52534,12 +52534,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Musician</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Raye</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -52548,28 +52548,28 @@
         </is>
       </c>
       <c r="E179">
-        <f>'MLS'!M25</f>
+        <f>'Musician'!M13</f>
         <v/>
       </c>
       <c r="F179">
-        <f>'MLS'!N25</f>
+        <f>'Musician'!N13</f>
         <v/>
       </c>
       <c r="G179">
-        <f>'MLS'!O25</f>
+        <f>'Musician'!O13</f>
         <v/>
       </c>
       <c r="H179" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2026 Cup: Kalshi 0.5%</t>
+          <t>Grammy EV 5.8 (raw 5.9, P(cap) 6%)</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>2026: 32 pts (as of 10-08; season ends Nov 7)</t>
+          <t>'WHERE IS MY HUSBAND!' ROTY/SOTY nominee</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -52579,7 +52579,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
+          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -52589,7 +52589,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>low confidence: far-out event</t>
+          <t>Overpriced by the field on award buzz: skip</t>
         </is>
       </c>
     </row>
@@ -52599,12 +52599,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Musician</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Raye</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -52613,28 +52613,23 @@
         </is>
       </c>
       <c r="E180">
-        <f>'Musician'!M14</f>
+        <f>'MLB'!M14</f>
         <v/>
       </c>
       <c r="F180">
-        <f>'Musician'!N14</f>
+        <f>'MLB'!N14</f>
         <v/>
       </c>
       <c r="G180">
-        <f>'Musician'!O14</f>
+        <f>'MLB'!O14</f>
         <v/>
       </c>
       <c r="H180" t="n">
         <v>3</v>
       </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>Grammy EV 5.8</t>
-        </is>
-      </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>'WHERE IS MY HUSBAND!' ROTY/SOTY nominee</t>
+          <t>2026: 86-76 (.5309)</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -52644,7 +52639,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
+          <t>2026 win% from league standings (A); title prob = model estimate — no 2027 World Series odds posted</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -52654,7 +52649,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>Overpriced by the field on award buzz: skip</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -52664,37 +52659,42 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Minnesota United FC</t>
+        </is>
+      </c>
+      <c r="D181" s="11" t="inlineStr">
+        <is>
+          <t>Wu</t>
         </is>
       </c>
       <c r="E181">
-        <f>'MLB'!M14</f>
+        <f>'MLS'!M26</f>
         <v/>
       </c>
       <c r="F181">
-        <f>'MLB'!N14</f>
+        <f>'MLS'!N26</f>
         <v/>
       </c>
       <c r="G181">
-        <f>'MLB'!O14</f>
+        <f>'MLS'!O26</f>
         <v/>
       </c>
       <c r="H181" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>2026 Cup: Kalshi 0.5%</t>
+        </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>2026: 86-76 (.5309)</t>
+          <t>2026: 29 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -52704,7 +52704,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026 win% from league standings (A); title prob = model estimate — no 2027 World Series odds posted</t>
+          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -52729,24 +52729,24 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Minnesota United FC</t>
-        </is>
-      </c>
-      <c r="D182" s="11" t="inlineStr">
-        <is>
-          <t>Wu</t>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E182">
-        <f>'MLS'!M26</f>
+        <f>'MLS'!M27</f>
         <v/>
       </c>
       <c r="F182">
-        <f>'MLS'!N26</f>
+        <f>'MLS'!N27</f>
         <v/>
       </c>
       <c r="G182">
-        <f>'MLS'!O26</f>
+        <f>'MLS'!O27</f>
         <v/>
       </c>
       <c r="H182" t="n">
@@ -52759,7 +52759,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>2026: 29 pts (as of 10-08; season ends Nov 7)</t>
+          <t>2026: 32 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -52794,7 +52794,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -52803,15 +52803,15 @@
         </is>
       </c>
       <c r="E183">
-        <f>'MLS'!M27</f>
+        <f>'MLS'!M28</f>
         <v/>
       </c>
       <c r="F183">
-        <f>'MLS'!N27</f>
+        <f>'MLS'!N28</f>
         <v/>
       </c>
       <c r="G183">
-        <f>'MLS'!O27</f>
+        <f>'MLS'!O28</f>
         <v/>
       </c>
       <c r="H183" t="n">
@@ -52824,7 +52824,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>2026: 32 pts (as of 10-08; season ends Nov 7)</t>
+          <t>2026: 31 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -52859,7 +52859,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>D.C. United</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -52868,15 +52868,15 @@
         </is>
       </c>
       <c r="E184">
-        <f>'MLS'!M28</f>
+        <f>'MLS'!M29</f>
         <v/>
       </c>
       <c r="F184">
-        <f>'MLS'!N28</f>
+        <f>'MLS'!N29</f>
         <v/>
       </c>
       <c r="G184">
-        <f>'MLS'!O28</f>
+        <f>'MLS'!O29</f>
         <v/>
       </c>
       <c r="H184" t="n">
@@ -52889,7 +52889,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>2026: 31 pts (as of 10-08; season ends Nov 7)</t>
+          <t>2026: 30 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -52924,24 +52924,24 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>D.C. United</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="D185" s="11" t="inlineStr">
+        <is>
+          <t>Fryar</t>
         </is>
       </c>
       <c r="E185">
-        <f>'MLS'!M29</f>
+        <f>'MLS'!M30</f>
         <v/>
       </c>
       <c r="F185">
-        <f>'MLS'!N29</f>
+        <f>'MLS'!N30</f>
         <v/>
       </c>
       <c r="G185">
-        <f>'MLS'!O29</f>
+        <f>'MLS'!O30</f>
         <v/>
       </c>
       <c r="H185" t="n">
@@ -52954,7 +52954,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>2026: 30 pts (as of 10-08; season ends Nov 7)</t>
+          <t>2026: 29 pts (as of 10-08; season ends Nov 7)</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -52984,42 +52984,42 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Musician</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
-        </is>
-      </c>
-      <c r="D186" s="11" t="inlineStr">
-        <is>
-          <t>Fryar</t>
+          <t>Rosalía</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E186">
-        <f>'MLS'!M30</f>
+        <f>'Musician'!M14</f>
         <v/>
       </c>
       <c r="F186">
-        <f>'MLS'!N30</f>
+        <f>'Musician'!N14</f>
         <v/>
       </c>
       <c r="G186">
-        <f>'MLS'!O30</f>
+        <f>'Musician'!O14</f>
         <v/>
       </c>
       <c r="H186" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2026 Cup: Kalshi 0.5%</t>
+          <t>Grammy EV 6.2 (raw 6.4, P(cap) 8%)</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>2026: 29 pts (as of 10-08; season ends Nov 7)</t>
+          <t>Lux (Grammy-driven pick; small Hot 100 profile)</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -53029,7 +53029,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026 points (league standings, A) + Kalshi KXMLSCUP-26 price as strength proxy, shrunk 50% toward the field</t>
+          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -53039,7 +53039,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>low confidence: far-out event</t>
+          <t>Overpriced by the field on award buzz: skip</t>
         </is>
       </c>
     </row>
@@ -58488,12 +58488,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Musician</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Ariana Grande</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -58502,34 +58502,38 @@
         </is>
       </c>
       <c r="E278">
-        <f>'Country'!M23</f>
+        <f>'Musician'!M16</f>
         <v/>
       </c>
       <c r="F278">
-        <f>'Country'!N23</f>
+        <f>'Musician'!N16</f>
         <v/>
       </c>
       <c r="G278">
-        <f>'Country'!O23</f>
+        <f>'Musician'!O16</f>
         <v/>
       </c>
       <c r="H278" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>IMF WEO Apr-2025: 5.8%</t>
-        </is>
-      </c>
-      <c r="J278" t="inlineStr"/>
+          <t>Grammy EV 2.7 (raw 2.7, P(cap) 0%)</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>'hate that i made you love me' #1 (Jun 2026); SOTY nom 35%</t>
+        </is>
+      </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
+          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -58537,7 +58541,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N278" t="inlineStr"/>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>late filler</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -58545,12 +58553,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -58559,33 +58567,34 @@
         </is>
       </c>
       <c r="E279">
-        <f>'MLB'!M33</f>
+        <f>'Country'!M23</f>
         <v/>
       </c>
       <c r="F279">
-        <f>'MLB'!N33</f>
+        <f>'Country'!N23</f>
         <v/>
       </c>
       <c r="G279">
-        <f>'MLB'!O33</f>
+        <f>'Country'!O23</f>
         <v/>
       </c>
       <c r="H279" t="n">
         <v>4</v>
       </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>2026: 62-100 (.3827)</t>
-        </is>
-      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>IMF WEO Apr-2025: 5.8%</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>2026 win% from league standings (A); title prob = model estimate — no 2027 World Series odds posted</t>
+          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -58593,11 +58602,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N279" t="inlineStr">
-        <is>
-          <t>low confidence: far-out event</t>
-        </is>
-      </c>
+      <c r="N279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -58605,42 +58610,37 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Musician</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Sabrina Carpenter</t>
-        </is>
-      </c>
-      <c r="D280" s="11" t="inlineStr">
-        <is>
-          <t>Jens</t>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E280">
-        <f>'Musician'!M16</f>
+        <f>'MLB'!M33</f>
         <v/>
       </c>
       <c r="F280">
-        <f>'Musician'!N16</f>
+        <f>'MLB'!N33</f>
         <v/>
       </c>
       <c r="G280">
-        <f>'Musician'!O16</f>
+        <f>'MLB'!O33</f>
         <v/>
       </c>
       <c r="H280" t="n">
-        <v>3</v>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>Grammy EV 1.0</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Man's Best Friend (Aug 2025) was last cycle; no successor found</t>
+          <t>2026: 62-100 (.3827)</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -58650,7 +58650,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>2027 Hot 100 baseline = my estimate; Grammy: estimate (C)</t>
+          <t>2026 win% from league standings (A); title prob = model estimate — no 2027 World Series odds posted</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -58660,7 +58660,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>late filler</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -58670,37 +58670,42 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>Musician</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>J.J. Spaun</t>
+          <t>Sabrina Carpenter</t>
         </is>
       </c>
       <c r="D281" s="11" t="inlineStr">
         <is>
-          <t>Mitchell</t>
+          <t>Jens</t>
         </is>
       </c>
       <c r="E281">
-        <f>'Golf'!M16</f>
+        <f>'Musician'!M17</f>
         <v/>
       </c>
       <c r="F281">
-        <f>'Golf'!N16</f>
+        <f>'Musician'!N17</f>
         <v/>
       </c>
       <c r="G281">
-        <f>'Golf'!O16</f>
+        <f>'Musician'!O17</f>
         <v/>
       </c>
       <c r="H281" t="n">
         <v>3</v>
       </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Grammy EV 1.0</t>
+        </is>
+      </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>OWGR 12 (2026-10-08)</t>
+          <t>Man's Best Friend (Aug 2025) was last cycle; no successor found</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -58710,7 +58715,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>OWGR rank from league standings pull (A); major-win probabilities = model (rank-weighted share of 4 majors)</t>
+          <t>2027 Hot 100 baseline = my estimate; Grammy: estimate (C)</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -58718,7 +58723,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N281" t="inlineStr"/>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>late filler</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -58726,42 +58735,37 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Musician</t>
+          <t>Golf</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Ariana Grande</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>J.J. Spaun</t>
+        </is>
+      </c>
+      <c r="D282" s="11" t="inlineStr">
+        <is>
+          <t>Mitchell</t>
         </is>
       </c>
       <c r="E282">
-        <f>'Musician'!M17</f>
+        <f>'Golf'!M16</f>
         <v/>
       </c>
       <c r="F282">
-        <f>'Musician'!N17</f>
+        <f>'Golf'!N16</f>
         <v/>
       </c>
       <c r="G282">
-        <f>'Musician'!O17</f>
+        <f>'Golf'!O16</f>
         <v/>
       </c>
       <c r="H282" t="n">
         <v>3</v>
       </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t>Grammy EV 2.6</t>
-        </is>
-      </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>'hate that i made you love me' #1 (Jun 2026); SOTY nom 35%</t>
+          <t>OWGR 12 (2026-10-08)</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -58771,7 +58775,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
+          <t>OWGR rank from league standings pull (A); major-win probabilities = model (rank-weighted share of 4 majors)</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -58779,11 +58783,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N282" t="inlineStr">
-        <is>
-          <t>late filler</t>
-        </is>
-      </c>
+      <c r="N282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -62677,12 +62677,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Actress</t>
+          <t>Musician</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Danielle Brooks</t>
+          <t>Phoebe Bridgers</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -62691,23 +62691,28 @@
         </is>
       </c>
       <c r="E349">
-        <f>'Actress'!M36</f>
+        <f>'Musician'!M19</f>
         <v/>
       </c>
       <c r="F349">
-        <f>'Actress'!N36</f>
+        <f>'Musician'!N19</f>
         <v/>
       </c>
       <c r="G349">
-        <f>'Actress'!O36</f>
+        <f>'Musician'!O19</f>
         <v/>
       </c>
       <c r="H349" t="n">
         <v>4</v>
       </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Grammy EV 4.0 (raw 4.0, P(cap) 2%)</t>
+        </is>
+      </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>A Minecraft Movie Squared (Jul 23)</t>
+          <t>Lost Weekend (AOTY nominee candidate)</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
@@ -62717,7 +62722,7 @@
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
@@ -62737,48 +62742,47 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Actress</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="D350" s="11" t="inlineStr">
-        <is>
-          <t>Molmen</t>
+          <t>Danielle Brooks</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>— free</t>
         </is>
       </c>
       <c r="E350">
-        <f>'Country'!M37</f>
+        <f>'Actress'!M36</f>
         <v/>
       </c>
       <c r="F350">
-        <f>'Country'!N37</f>
+        <f>'Actress'!N36</f>
         <v/>
       </c>
       <c r="G350">
-        <f>'Country'!O37</f>
+        <f>'Actress'!O36</f>
         <v/>
       </c>
       <c r="H350" t="n">
         <v>4</v>
       </c>
-      <c r="I350" t="inlineStr">
-        <is>
-          <t>IMF WEO Apr-2025: 4.0%</t>
-        </is>
-      </c>
-      <c r="J350" t="inlineStr"/>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>A Minecraft Movie Squared (Jul 23)</t>
+        </is>
+      </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
@@ -62786,7 +62790,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N350" t="inlineStr"/>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>late filler</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -62794,47 +62802,48 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Actor</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Jack Black</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>— free</t>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D351" s="11" t="inlineStr">
+        <is>
+          <t>Molmen</t>
         </is>
       </c>
       <c r="E351">
-        <f>'Actor'!M69</f>
+        <f>'Country'!M37</f>
         <v/>
       </c>
       <c r="F351">
-        <f>'Actor'!N69</f>
+        <f>'Country'!N37</f>
         <v/>
       </c>
       <c r="G351">
-        <f>'Actor'!O69</f>
+        <f>'Country'!O37</f>
         <v/>
       </c>
       <c r="H351" t="n">
         <v>4</v>
       </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>A Minecraft Movie Squared (Jul 23)</t>
-        </is>
-      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>IMF WEO Apr-2025: 4.0%</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -62842,11 +62851,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N351" t="inlineStr">
-        <is>
-          <t>late filler</t>
-        </is>
-      </c>
+      <c r="N351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -62854,12 +62859,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Actress</t>
+          <t>Actor</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Jennifer Coolidge</t>
+          <t>Jack Black</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -62868,15 +62873,15 @@
         </is>
       </c>
       <c r="E352">
-        <f>'Actress'!M37</f>
+        <f>'Actor'!M69</f>
         <v/>
       </c>
       <c r="F352">
-        <f>'Actress'!N37</f>
+        <f>'Actor'!N69</f>
         <v/>
       </c>
       <c r="G352">
-        <f>'Actress'!O37</f>
+        <f>'Actor'!O69</f>
         <v/>
       </c>
       <c r="H352" t="n">
@@ -62914,12 +62919,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>NCAAF</t>
+          <t>Actress</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>Jennifer Coolidge</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -62928,38 +62933,33 @@
         </is>
       </c>
       <c r="E353">
-        <f>'NCAAF'!M13</f>
+        <f>'Actress'!M37</f>
         <v/>
       </c>
       <c r="F353">
-        <f>'NCAAF'!N13</f>
+        <f>'Actress'!N37</f>
         <v/>
       </c>
       <c r="G353">
-        <f>'NCAAF'!O13</f>
+        <f>'Actress'!O37</f>
         <v/>
       </c>
       <c r="H353" t="n">
-        <v>3</v>
-      </c>
-      <c r="I353" t="inlineStr">
-        <is>
-          <t>Kalshi 4.5%</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>AP #10, 4-1, SEC</t>
+          <t>A Minecraft Movie Squared (Jul 23)</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>KXNCAAF-27 exchange mid-price, pulled 2026-10-08</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
@@ -62967,7 +62967,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N353" t="inlineStr"/>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>late filler</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -62975,12 +62979,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>NCAAF</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -62989,34 +62993,38 @@
         </is>
       </c>
       <c r="E354">
-        <f>'Country'!M38</f>
+        <f>'NCAAF'!M13</f>
         <v/>
       </c>
       <c r="F354">
-        <f>'Country'!N38</f>
+        <f>'NCAAF'!N13</f>
         <v/>
       </c>
       <c r="G354">
-        <f>'Country'!O38</f>
+        <f>'NCAAF'!O13</f>
         <v/>
       </c>
       <c r="H354" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>IMF WEO Apr-2025: 5.0%</t>
-        </is>
-      </c>
-      <c r="J354" t="inlineStr"/>
+          <t>Kalshi 4.5%</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>AP #10, 4-1, SEC</t>
+        </is>
+      </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
+          <t>KXNCAAF-27 exchange mid-price, pulled 2026-10-08</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
@@ -63032,12 +63040,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Musician</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Phoebe Bridgers</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -63046,15 +63054,15 @@
         </is>
       </c>
       <c r="E355">
-        <f>'Musician'!M19</f>
+        <f>'Country'!M38</f>
         <v/>
       </c>
       <c r="F355">
-        <f>'Musician'!N19</f>
+        <f>'Country'!N38</f>
         <v/>
       </c>
       <c r="G355">
-        <f>'Musician'!O19</f>
+        <f>'Country'!O38</f>
         <v/>
       </c>
       <c r="H355" t="n">
@@ -63062,22 +63070,18 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>Grammy EV 3.9</t>
-        </is>
-      </c>
-      <c r="J355" t="inlineStr">
-        <is>
-          <t>Lost Weekend (AOTY nominee candidate)</t>
-        </is>
-      </c>
+          <t>IMF WEO Apr-2025: 5.0%</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
+          <t>IMF WEO April 2025 vintage via DBnomics (api.db.nomics.world, pulled by Actions runner 2026-10-08), series NGDP_RPCH 2027. STALE vintage: Oct 13 2026 WEO replaces it; the 2025-10 and 2026-04 vintages are not mirrored.</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
@@ -63085,11 +63089,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N355" t="inlineStr">
-        <is>
-          <t>late filler</t>
-        </is>
-      </c>
+      <c r="N355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -65931,12 +65931,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Musician</t>
+          <t>NCAAB</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Sienna Spiro</t>
+          <t>Creighton</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -65945,30 +65945,21 @@
         </is>
       </c>
       <c r="E404">
-        <f>'Musician'!M22</f>
+        <f>'NCAAB'!M30</f>
         <v/>
       </c>
       <c r="F404">
-        <f>'Musician'!N22</f>
+        <f>'NCAAB'!N30</f>
         <v/>
       </c>
       <c r="G404">
-        <f>'Musician'!O22</f>
+        <f>'NCAAB'!O30</f>
         <v/>
       </c>
       <c r="H404" t="n">
         <v>4</v>
       </c>
-      <c r="I404" t="inlineStr">
-        <is>
-          <t>Grammy EV 3.0</t>
-        </is>
-      </c>
-      <c r="J404" t="inlineStr">
-        <is>
-          <t>Best New Artist candidate (nom 89.5%, win 26%)</t>
-        </is>
-      </c>
+      <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr">
         <is>
           <t>C</t>
@@ -65976,7 +65967,7 @@
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="M404" t="inlineStr">
@@ -65986,7 +65977,7 @@
       </c>
       <c r="N404" t="inlineStr">
         <is>
-          <t>late filler</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -65996,12 +65987,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>NCAAB</t>
+          <t>Actress</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Creighton</t>
+          <t>Kate O'Flynn</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -66010,21 +66001,25 @@
         </is>
       </c>
       <c r="E405">
-        <f>'NCAAB'!M30</f>
+        <f>'Actress'!M46</f>
         <v/>
       </c>
       <c r="F405">
-        <f>'NCAAB'!N30</f>
+        <f>'Actress'!N46</f>
         <v/>
       </c>
       <c r="G405">
-        <f>'NCAAB'!O30</f>
+        <f>'Actress'!O46</f>
         <v/>
       </c>
       <c r="H405" t="n">
         <v>4</v>
       </c>
-      <c r="J405" t="inlineStr"/>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>no 2027 film found in Wikipedia's cast lists</t>
+        </is>
+      </c>
       <c r="K405" t="inlineStr">
         <is>
           <t>C</t>
@@ -66032,7 +66027,7 @@
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M405" t="inlineStr">
@@ -66042,7 +66037,7 @@
       </c>
       <c r="N405" t="inlineStr">
         <is>
-          <t>low confidence: far-out event</t>
+          <t>late filler</t>
         </is>
       </c>
     </row>
@@ -66052,12 +66047,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Actress</t>
+          <t>NCAAB</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Kate O'Flynn</t>
+          <t>Baylor</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -66066,25 +66061,21 @@
         </is>
       </c>
       <c r="E406">
-        <f>'Actress'!M46</f>
+        <f>'NCAAB'!M31</f>
         <v/>
       </c>
       <c r="F406">
-        <f>'Actress'!N46</f>
+        <f>'NCAAB'!N31</f>
         <v/>
       </c>
       <c r="G406">
-        <f>'Actress'!O46</f>
+        <f>'NCAAB'!O31</f>
         <v/>
       </c>
       <c r="H406" t="n">
         <v>4</v>
       </c>
-      <c r="J406" t="inlineStr">
-        <is>
-          <t>no 2027 film found in Wikipedia's cast lists</t>
-        </is>
-      </c>
+      <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
           <t>C</t>
@@ -66092,7 +66083,7 @@
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="M406" t="inlineStr">
@@ -66102,7 +66093,7 @@
       </c>
       <c r="N406" t="inlineStr">
         <is>
-          <t>late filler</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -66112,12 +66103,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>NCAAB</t>
+          <t>Actor</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>Sebastian Stan</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -66126,21 +66117,25 @@
         </is>
       </c>
       <c r="E407">
-        <f>'NCAAB'!M31</f>
+        <f>'Actor'!M86</f>
         <v/>
       </c>
       <c r="F407">
-        <f>'NCAAB'!N31</f>
+        <f>'Actor'!N86</f>
         <v/>
       </c>
       <c r="G407">
-        <f>'NCAAB'!O31</f>
+        <f>'Actor'!O86</f>
         <v/>
       </c>
       <c r="H407" t="n">
         <v>4</v>
       </c>
-      <c r="J407" t="inlineStr"/>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>no 2027 film found in Wikipedia's cast lists</t>
+        </is>
+      </c>
       <c r="K407" t="inlineStr">
         <is>
           <t>C</t>
@@ -66148,7 +66143,7 @@
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
         </is>
       </c>
       <c r="M407" t="inlineStr">
@@ -66158,7 +66153,7 @@
       </c>
       <c r="N407" t="inlineStr">
         <is>
-          <t>low confidence: far-out event</t>
+          <t>late filler</t>
         </is>
       </c>
     </row>
@@ -66168,12 +66163,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Actor</t>
+          <t>NCAAB</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Sebastian Stan</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -66182,25 +66177,21 @@
         </is>
       </c>
       <c r="E408">
-        <f>'Actor'!M86</f>
+        <f>'NCAAB'!M32</f>
         <v/>
       </c>
       <c r="F408">
-        <f>'Actor'!N86</f>
+        <f>'NCAAB'!N32</f>
         <v/>
       </c>
       <c r="G408">
-        <f>'Actor'!O86</f>
+        <f>'NCAAB'!O32</f>
         <v/>
       </c>
       <c r="H408" t="n">
         <v>4</v>
       </c>
-      <c r="J408" t="inlineStr">
-        <is>
-          <t>no 2027 film found in Wikipedia's cast lists</t>
-        </is>
-      </c>
+      <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr">
         <is>
           <t>C</t>
@@ -66208,7 +66199,7 @@
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>Wikipedia 'List of American films of 2027' casts (Actions-runner pull 2026-10-08) x comp-based box office/RT estimates; cast lists are billed leads only (cameos not captured)</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="M408" t="inlineStr">
@@ -66218,7 +66209,7 @@
       </c>
       <c r="N408" t="inlineStr">
         <is>
-          <t>late filler</t>
+          <t>low confidence: far-out event</t>
         </is>
       </c>
     </row>
@@ -66228,12 +66219,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>NCAAB</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Arthur Fils</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -66242,21 +66233,25 @@
         </is>
       </c>
       <c r="E409">
-        <f>'NCAAB'!M32</f>
+        <f>'Tennis'!M25</f>
         <v/>
       </c>
       <c r="F409">
-        <f>'NCAAB'!N32</f>
+        <f>'Tennis'!N25</f>
         <v/>
       </c>
       <c r="G409">
-        <f>'NCAAB'!O32</f>
+        <f>'Tennis'!O25</f>
         <v/>
       </c>
       <c r="H409" t="n">
         <v>4</v>
       </c>
-      <c r="J409" t="inlineStr"/>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>ATP 11 (2026-10-08)</t>
+        </is>
+      </c>
       <c r="K409" t="inlineStr">
         <is>
           <t>C</t>
@@ -66264,7 +66259,7 @@
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>ATP rank from league standings pull (A) / WTA via Olympics.com Oct 5; AO odds VegasInsider/Johnnybet Oct 2026; probabilities = agent estimates</t>
         </is>
       </c>
       <c r="M409" t="inlineStr">
@@ -66272,11 +66267,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N409" t="inlineStr">
-        <is>
-          <t>low confidence: far-out event</t>
-        </is>
-      </c>
+      <c r="N409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -66284,12 +66275,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>Musician</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Arthur Fils</t>
+          <t>Sienna Spiro</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -66298,23 +66289,28 @@
         </is>
       </c>
       <c r="E410">
-        <f>'Tennis'!M25</f>
+        <f>'Musician'!M22</f>
         <v/>
       </c>
       <c r="F410">
-        <f>'Tennis'!N25</f>
+        <f>'Musician'!N22</f>
         <v/>
       </c>
       <c r="G410">
-        <f>'Tennis'!O25</f>
+        <f>'Musician'!O22</f>
         <v/>
       </c>
       <c r="H410" t="n">
         <v>4</v>
       </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Grammy EV 2.9 (raw 2.9, P(cap) 0%)</t>
+        </is>
+      </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>ATP 11 (2026-10-08)</t>
+          <t>Best New Artist candidate (nom 89.5%, win 26%)</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
@@ -66324,7 +66320,7 @@
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>ATP rank from league standings pull (A) / WTA via Olympics.com Oct 5; AO odds VegasInsider/Johnnybet Oct 2026; probabilities = agent estimates</t>
+          <t>2027 Hot 100 baseline = my estimate; Grammy: Kalshi KXGRAM*-69 prices (A) + estimates for other categories (C)</t>
         </is>
       </c>
       <c r="M410" t="inlineStr">
@@ -66332,7 +66328,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="N410" t="inlineStr"/>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>late filler</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
